--- a/현황1.xlsx
+++ b/현황1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python\Python314\py_work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B88DE37-5894-438D-A1B6-53603D5E60D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E992ACEC-BBCF-480C-A539-808802F24360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29385" yWindow="3165" windowWidth="26925" windowHeight="16905" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30945" yWindow="3030" windowWidth="29985" windowHeight="19245" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="맵핑" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="650">
   <si>
     <t>031-123-3469</t>
   </si>
@@ -382,10 +382,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>장철호가구공방</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>경기 용인시 수지구 수지로227번길8</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -394,18 +390,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>장철호대표</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>010-3874-9397</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>031-266-7724</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>담당자이메일</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1978,14 +1966,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>특화 기계</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>특화 화학</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>회사</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2018,15 +1998,19 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>특화 목재</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>퀵패스</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>모니터링</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>장철호가구공방1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>장철호 대표1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2431,7 +2415,7 @@
     <col min="5" max="5" width="11.25" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20" style="1" customWidth="1"/>
     <col min="7" max="7" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="37.625" style="1" customWidth="1"/>
     <col min="9" max="9" width="23.375" style="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.625" style="1" bestFit="1" customWidth="1"/>
@@ -2448,7 +2432,7 @@
         <v>87</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>86</v>
@@ -2484,7 +2468,7 @@
         <v>112</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>77</v>
@@ -2502,10 +2486,10 @@
         <v>74</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
@@ -2515,41 +2499,35 @@
       <c r="B2" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="L2" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
@@ -2559,31 +2537,34 @@
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="7" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>648</v>
+        <v>643</v>
+      </c>
+      <c r="S3" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
@@ -2597,7 +2578,7 @@
         <v>73</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>4</v>
@@ -2618,10 +2599,10 @@
         <v>63</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="R4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" s="1">
         <v>1</v>
@@ -2638,7 +2619,7 @@
         <v>69</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>68</v>
@@ -2659,13 +2640,10 @@
         <v>63</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>88</v>
+        <v>539</v>
       </c>
       <c r="R5" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S5" s="1">
         <v>0</v>
@@ -2682,7 +2660,7 @@
         <v>62</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>61</v>
@@ -2703,13 +2681,10 @@
         <v>57</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>88</v>
+        <v>540</v>
       </c>
       <c r="R6" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S6" s="1">
         <v>0</v>
@@ -2726,7 +2701,7 @@
         <v>56</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>4</v>
@@ -2747,13 +2722,16 @@
         <v>53</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>100</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>90</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="R7" s="1">
         <v>0</v>
@@ -2773,7 +2751,7 @@
         <v>52</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>4</v>
@@ -2792,7 +2770,7 @@
         <v>49</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>101</v>
@@ -2801,7 +2779,7 @@
         <v>91</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="R8" s="1">
         <v>0</v>
@@ -2821,7 +2799,7 @@
         <v>48</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>47</v>
@@ -2840,7 +2818,7 @@
         <v>43</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>102</v>
@@ -2849,7 +2827,7 @@
         <v>92</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="R9" s="1">
         <v>0</v>
@@ -2869,7 +2847,7 @@
         <v>42</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>4</v>
@@ -2890,7 +2868,7 @@
         <v>39</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>103</v>
@@ -2899,16 +2877,13 @@
         <v>93</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="R10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="1">
         <v>0</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
@@ -2921,7 +2896,7 @@
       <c r="C11" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E11" s="7" t="s">
@@ -2943,7 +2918,7 @@
         <v>34</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>104</v>
@@ -2952,16 +2927,13 @@
         <v>94</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="R11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S11" s="1">
         <v>0</v>
-      </c>
-      <c r="T11" s="1" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
@@ -2974,7 +2946,7 @@
       <c r="C12" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E12" s="7" t="s">
@@ -2996,7 +2968,7 @@
         <v>30</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>105</v>
@@ -3005,10 +2977,10 @@
         <v>95</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="R12" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S12" s="1">
         <v>0</v>
@@ -3024,7 +2996,7 @@
       <c r="C13" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E13" s="7" t="s">
@@ -3046,17 +3018,17 @@
         <v>24</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2" t="s">
         <v>96</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="R13" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S13" s="1">
         <v>1</v>
@@ -3072,7 +3044,7 @@
       <c r="C14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E14" s="8" t="s">
@@ -3094,17 +3066,17 @@
         <v>19</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2" t="s">
         <v>97</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="R14" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S14" s="1">
         <v>0</v>
@@ -3120,7 +3092,7 @@
       <c r="C15" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E15" s="8" t="s">
@@ -3142,15 +3114,15 @@
         <v>15</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="Q15" s="1" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="R15" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="S15" s="1">
         <v>0</v>
@@ -3166,7 +3138,7 @@
       <c r="C16" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E16" s="8" t="s">
@@ -3188,24 +3160,21 @@
         <v>11</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="Q16" s="1" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="R16" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S16" s="1">
         <v>1</v>
       </c>
-      <c r="T16" s="1" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -3215,7 +3184,7 @@
       <c r="C17" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E17" s="8" t="s">
@@ -3237,23 +3206,23 @@
         <v>0</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>106</v>
       </c>
       <c r="M17" s="2"/>
       <c r="Q17" s="1" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="R17" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S17" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -3263,8 +3232,8 @@
       <c r="C18" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>642</v>
+      <c r="D18" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>4</v>
@@ -3282,26 +3251,26 @@
         <v>1</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>107</v>
       </c>
       <c r="M18" s="2"/>
       <c r="Q18" s="1" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="R18" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S18" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -3309,31 +3278,31 @@
         <v>1</v>
       </c>
       <c r="C19" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="G19" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>642</v>
-      </c>
-      <c r="E19" s="8" t="s">
+      <c r="H19" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="I19" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>135</v>
-      </c>
       <c r="K19" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>108</v>
@@ -3343,13 +3312,13 @@
         <v>88</v>
       </c>
       <c r="R19" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S19" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -3357,31 +3326,31 @@
         <v>1</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>642</v>
+        <v>133</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I20" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>109</v>
@@ -3389,9 +3358,6 @@
       <c r="M20" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="Q20" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="R20" s="1">
         <v>0</v>
       </c>
@@ -3399,7 +3365,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -3407,31 +3373,31 @@
         <v>1</v>
       </c>
       <c r="C21" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="G21" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="E21" s="8" t="s">
+      <c r="H21" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="I21" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="J21" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="H21" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>146</v>
-      </c>
       <c r="K21" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>110</v>
@@ -3446,7 +3412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -3454,31 +3420,34 @@
         <v>1</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>641</v>
+        <v>144</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F22" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="J22" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="G22" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>151</v>
-      </c>
       <c r="K22" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="R22" s="1">
         <v>0</v>
@@ -3487,7 +3456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -3495,31 +3464,34 @@
         <v>1</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>641</v>
+        <v>149</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F23" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="J23" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="G23" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>156</v>
-      </c>
       <c r="K23" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="R23" s="1">
         <v>0</v>
@@ -3528,7 +3500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -3536,31 +3508,34 @@
         <v>1</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="D24" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I24" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="R24" s="1">
         <v>0</v>
@@ -3569,7 +3544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -3577,40 +3552,43 @@
         <v>1</v>
       </c>
       <c r="C25" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="G25" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E25" s="8" t="s">
+      <c r="H25" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="I25" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J25" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="G25" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="K25" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="R25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -3618,40 +3596,43 @@
         <v>1</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="D26" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I26" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="R26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -3659,40 +3640,43 @@
         <v>1</v>
       </c>
       <c r="C27" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="G27" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="D27" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E27" s="8" t="s">
+      <c r="H27" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="I27" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="G27" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>176</v>
-      </c>
       <c r="K27" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="R27" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S27" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -3700,43 +3684,43 @@
         <v>1</v>
       </c>
       <c r="C28" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G28" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="D28" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E28" s="8" t="s">
+      <c r="H28" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="I28" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J28" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="G28" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>182</v>
-      </c>
       <c r="K28" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="R28" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S28" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -3744,43 +3728,43 @@
         <v>1</v>
       </c>
       <c r="C29" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="G29" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D29" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E29" s="8" t="s">
+      <c r="H29" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="I29" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="J29" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="H29" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>189</v>
-      </c>
       <c r="K29" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="R29" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S29" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -3788,46 +3772,43 @@
         <v>1</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="D30" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="R30" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S30" s="1">
         <v>0</v>
       </c>
-      <c r="T30" s="1" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -3835,43 +3816,43 @@
         <v>1</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="D31" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="R31" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="S31" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -3879,43 +3860,37 @@
         <v>1</v>
       </c>
       <c r="C32" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="G32" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="E32" s="8" t="s">
+      <c r="H32" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="I32" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="J32" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="H32" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>204</v>
-      </c>
       <c r="K32" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>127</v>
+        <v>566</v>
       </c>
       <c r="R32" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S32" s="1">
         <v>1</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
@@ -3926,37 +3901,34 @@
         <v>1</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>651</v>
+        <v>202</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>128</v>
+        <v>567</v>
       </c>
       <c r="R33" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S33" s="1">
         <v>0</v>
@@ -3967,37 +3939,34 @@
         <v>32</v>
       </c>
       <c r="B34" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G34" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="D34" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="E34" s="8" t="s">
+      <c r="H34" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="I34" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="J34" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="G34" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>214</v>
-      </c>
       <c r="K34" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="Q34" s="1" t="s">
-        <v>128</v>
+        <v>568</v>
       </c>
       <c r="R34" s="1">
         <v>0</v>
@@ -4011,37 +3980,34 @@
         <v>33</v>
       </c>
       <c r="B35" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>651</v>
+        <v>212</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>20</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="Q35" s="1" t="s">
-        <v>88</v>
+        <v>569</v>
       </c>
       <c r="R35" s="1">
         <v>0</v>
@@ -4055,37 +4021,37 @@
         <v>34</v>
       </c>
       <c r="B36" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G36" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="D36" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="E36" s="8" t="s">
+      <c r="H36" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="F36" s="8" t="s">
+      <c r="I36" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J36" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="G36" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>224</v>
-      </c>
       <c r="K36" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="R36" s="1">
         <v>0</v>
@@ -4099,37 +4065,37 @@
         <v>35</v>
       </c>
       <c r="B37" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>651</v>
+        <v>222</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="R37" s="1">
         <v>0</v>
@@ -4143,46 +4109,43 @@
         <v>36</v>
       </c>
       <c r="B38" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="G38" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="D38" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="E38" s="8" t="s">
+      <c r="H38" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="I38" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J38" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="G38" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>234</v>
-      </c>
       <c r="K38" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="R38" s="1">
         <v>0</v>
       </c>
       <c r="S38" s="1">
         <v>0</v>
-      </c>
-      <c r="T38" s="1" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
@@ -4190,46 +4153,43 @@
         <v>37</v>
       </c>
       <c r="B39" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="D39" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="Q39" s="1" t="s">
         <v>124</v>
       </c>
       <c r="R39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" s="1">
         <v>0</v>
-      </c>
-      <c r="T39" s="1" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.3">
@@ -4237,34 +4197,34 @@
         <v>38</v>
       </c>
       <c r="B40" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="D40" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D40" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="Q40" s="1" t="s">
         <v>124</v>
@@ -4281,46 +4241,44 @@
         <v>39</v>
       </c>
       <c r="B41" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="D41" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D41" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E41" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="M41" s="2" t="s">
-        <v>90</v>
-      </c>
+      <c r="M41" s="2"/>
       <c r="Q41" s="1" t="s">
         <v>124</v>
       </c>
       <c r="R41" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S41" s="1">
         <v>1</v>
@@ -4331,49 +4289,49 @@
         <v>40</v>
       </c>
       <c r="B42" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="D42" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M42" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="Q42" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" s="1">
         <v>0</v>
+      </c>
+      <c r="T42" s="1" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.3">
@@ -4381,52 +4339,49 @@
         <v>41</v>
       </c>
       <c r="B43" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="D43" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="D43" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="M43" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="Q43" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R43" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S43" s="1">
         <v>0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
@@ -4434,49 +4389,50 @@
         <v>42</v>
       </c>
       <c r="B44" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="D44" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D44" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I44" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="M44" s="2" t="s">
-        <v>93</v>
-      </c>
+      <c r="M44" s="2"/>
       <c r="Q44" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R44" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S44" s="1">
         <v>0</v>
+      </c>
+      <c r="T44" s="1" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
@@ -4484,52 +4440,49 @@
         <v>43</v>
       </c>
       <c r="B45" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="D45" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D45" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I45" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="M45" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="Q45" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R45" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S45" s="1">
         <v>1</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
@@ -4537,49 +4490,49 @@
         <v>44</v>
       </c>
       <c r="B46" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="D46" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="D46" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="I46" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="M46" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="Q46" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R46" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S46" s="1">
         <v>0</v>
+      </c>
+      <c r="T46" s="1" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.3">
@@ -4587,44 +4540,42 @@
         <v>45</v>
       </c>
       <c r="B47" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G47" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="D47" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E47" s="8" t="s">
+      <c r="H47" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="I47" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J47" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="G47" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>272</v>
-      </c>
       <c r="K47" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="L47" s="2"/>
-      <c r="M47" s="2" t="s">
-        <v>96</v>
-      </c>
+      <c r="M47" s="2"/>
       <c r="Q47" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="R47" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="S47" s="1">
         <v>0</v>
@@ -4635,184 +4586,176 @@
         <v>46</v>
       </c>
       <c r="B48" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C48" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="G48" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="D48" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E48" s="8" t="s">
+      <c r="H48" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="F48" s="8" t="s">
+      <c r="I48" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J48" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="G48" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="I48" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>278</v>
-      </c>
       <c r="K48" s="2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="L48" s="2"/>
-      <c r="M48" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="Q48" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="R48" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S48" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>47</v>
       </c>
       <c r="B49" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
       <c r="Q49" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="R49" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S49" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>48</v>
       </c>
       <c r="B50" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="I50" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
       <c r="Q50" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="R50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" s="1">
         <v>0</v>
       </c>
-      <c r="T50" s="1" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>49</v>
       </c>
       <c r="B51" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="G51" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="D51" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E51" s="8" t="s">
+      <c r="H51" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="F51" s="8" t="s">
+      <c r="I51" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J51" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="G51" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="H51" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="I51" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>292</v>
-      </c>
       <c r="K51" s="2" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="M51" s="2"/>
       <c r="Q51" s="1" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="R51" s="1">
         <v>0</v>
@@ -4821,46 +4764,45 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>50</v>
       </c>
       <c r="B52" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="G52" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="D52" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E52" s="8" t="s">
+      <c r="H52" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="F52" s="8" t="s">
+      <c r="I52" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J52" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="G52" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="H52" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J52" s="7" t="s">
-        <v>298</v>
-      </c>
       <c r="K52" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="M52" s="2"/>
       <c r="Q52" s="1" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="R52" s="1">
         <v>0</v>
@@ -4869,46 +4811,46 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>51</v>
       </c>
       <c r="B53" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>108</v>
       </c>
       <c r="M53" s="2"/>
       <c r="Q53" s="1" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="R53" s="1">
         <v>0</v>
@@ -4917,48 +4859,45 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>52</v>
       </c>
       <c r="B54" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I54" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="M54" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="Q54" s="1" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="R54" s="1">
         <v>0</v>
@@ -4967,92 +4906,90 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>53</v>
       </c>
       <c r="B55" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="G55" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="D55" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E55" s="8" t="s">
+      <c r="H55" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="F55" s="8" t="s">
+      <c r="I55" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J55" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="G55" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="H55" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="I55" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J55" s="7" t="s">
-        <v>312</v>
-      </c>
       <c r="K55" s="2" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="M55" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="Q55" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>54</v>
       </c>
       <c r="B56" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I56" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>593</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="M56" s="2"/>
       <c r="Q56" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R56" s="1">
         <v>0</v>
@@ -5060,87 +4997,87 @@
       <c r="S56" s="1">
         <v>0</v>
       </c>
-      <c r="T56" s="1" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>55</v>
       </c>
       <c r="B57" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R57" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S57" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>56</v>
       </c>
       <c r="B58" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
+      </c>
+      <c r="Q58" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="R58" s="1">
         <v>0</v>
@@ -5149,262 +5086,265 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>57</v>
       </c>
       <c r="B59" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C59" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="G59" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="D59" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E59" s="8" t="s">
+      <c r="H59" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="F59" s="8" t="s">
+      <c r="I59" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J59" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="G59" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="H59" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="I59" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J59" s="7" t="s">
-        <v>330</v>
-      </c>
       <c r="K59" s="2" t="s">
-        <v>596</v>
+        <v>593</v>
+      </c>
+      <c r="Q59" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="R59" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S59" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>58</v>
       </c>
       <c r="B60" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E60" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="I60" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
+      </c>
+      <c r="Q60" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="R60" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S60" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>59</v>
       </c>
       <c r="B61" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C61" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="G61" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="D61" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E61" s="8" t="s">
+      <c r="H61" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="F61" s="8" t="s">
+      <c r="I61" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="J61" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="G61" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="H61" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="I61" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="J61" s="7" t="s">
-        <v>339</v>
-      </c>
       <c r="K61" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="R61" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S61" s="1">
         <v>1</v>
       </c>
-      <c r="T61" s="1" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>60</v>
       </c>
       <c r="B62" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C62" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="G62" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="D62" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E62" s="8" t="s">
+      <c r="H62" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="F62" s="8" t="s">
+      <c r="I62" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J62" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="G62" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="H62" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="I62" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J62" s="7" t="s">
-        <v>345</v>
-      </c>
       <c r="K62" s="2" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="R62" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S62" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>61</v>
       </c>
       <c r="B63" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="Q63" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="R63" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="S63" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>62</v>
       </c>
       <c r="B64" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C64" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="G64" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="D64" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E64" s="8" t="s">
+      <c r="H64" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="F64" s="8" t="s">
+      <c r="I64" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J64" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="G64" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="H64" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="I64" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J64" s="7" t="s">
-        <v>354</v>
-      </c>
       <c r="K64" s="2" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="R64" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S64" s="1">
         <v>1</v>
@@ -5415,43 +5355,46 @@
         <v>63</v>
       </c>
       <c r="B65" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="R65" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S65" s="1">
         <v>0</v>
+      </c>
+      <c r="T65" s="1" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.3">
@@ -5459,46 +5402,46 @@
         <v>64</v>
       </c>
       <c r="B66" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E66" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="I66" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="R66" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S66" s="1">
         <v>0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.3">
@@ -5506,43 +5449,46 @@
         <v>65</v>
       </c>
       <c r="B67" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="R67" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S67" s="1">
         <v>0</v>
+      </c>
+      <c r="T67" s="1" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.3">
@@ -5550,37 +5496,34 @@
         <v>66</v>
       </c>
       <c r="B68" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C68" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="G68" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="D68" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E68" s="8" t="s">
+      <c r="H68" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="F68" s="8" t="s">
+      <c r="I68" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J68" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="G68" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="H68" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="I68" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J68" s="7" t="s">
-        <v>372</v>
-      </c>
       <c r="K68" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="Q68" s="1" t="s">
-        <v>88</v>
+        <v>602</v>
       </c>
       <c r="R68" s="1">
         <v>0</v>
@@ -5594,46 +5537,40 @@
         <v>67</v>
       </c>
       <c r="B69" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I69" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="Q69" s="1" t="s">
-        <v>88</v>
+        <v>603</v>
       </c>
       <c r="R69" s="1">
         <v>0</v>
       </c>
       <c r="S69" s="1">
         <v>0</v>
-      </c>
-      <c r="T69" s="1" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.3">
@@ -5641,37 +5578,34 @@
         <v>68</v>
       </c>
       <c r="B70" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F70" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="J70" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="G70" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="H70" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="I70" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="J70" s="7" t="s">
-        <v>381</v>
-      </c>
       <c r="K70" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="Q70" s="1" t="s">
-        <v>88</v>
+        <v>604</v>
       </c>
       <c r="R70" s="1">
         <v>0</v>
@@ -5685,46 +5619,43 @@
         <v>69</v>
       </c>
       <c r="B71" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E71" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="R71" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" s="1">
         <v>0</v>
-      </c>
-      <c r="T71" s="1" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.3">
@@ -5732,37 +5663,37 @@
         <v>70</v>
       </c>
       <c r="B72" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C72" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="G72" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="D72" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E72" s="8" t="s">
+      <c r="H72" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="F72" s="8" t="s">
+      <c r="I72" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J72" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="G72" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="H72" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="I72" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J72" s="7" t="s">
-        <v>391</v>
-      </c>
       <c r="K72" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="R72" s="1">
         <v>0</v>
@@ -5776,40 +5707,40 @@
         <v>71</v>
       </c>
       <c r="B73" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="R73" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S73" s="1">
         <v>1</v>
@@ -5820,37 +5751,37 @@
         <v>72</v>
       </c>
       <c r="B74" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="R74" s="1">
         <v>0</v>
@@ -5864,40 +5795,40 @@
         <v>73</v>
       </c>
       <c r="B75" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C75" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="G75" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="D75" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E75" s="8" t="s">
+      <c r="H75" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="F75" s="8" t="s">
+      <c r="I75" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="J75" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="G75" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="H75" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="I75" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="J75" s="7" t="s">
-        <v>405</v>
-      </c>
       <c r="K75" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="R75" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S75" s="1">
         <v>0</v>
@@ -5908,40 +5839,40 @@
         <v>74</v>
       </c>
       <c r="B76" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="R76" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S76" s="1">
         <v>0</v>
@@ -5952,40 +5883,40 @@
         <v>75</v>
       </c>
       <c r="B77" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="R77" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S77" s="1">
         <v>1</v>
@@ -5996,40 +5927,40 @@
         <v>76</v>
       </c>
       <c r="B78" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="R78" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S78" s="1">
         <v>0</v>
@@ -6040,40 +5971,40 @@
         <v>77</v>
       </c>
       <c r="B79" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C79" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="G79" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="D79" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E79" s="8" t="s">
+      <c r="H79" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="F79" s="8" t="s">
+      <c r="I79" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J79" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="G79" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="H79" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="I79" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J79" s="7" t="s">
-        <v>423</v>
-      </c>
       <c r="K79" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="Q79" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="R79" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="S79" s="1">
         <v>0</v>
@@ -6084,46 +6015,43 @@
         <v>78</v>
       </c>
       <c r="B80" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E80" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="H80" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J80" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="F80" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="G80" s="8" t="s">
-        <v>425</v>
-      </c>
-      <c r="H80" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="I80" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J80" s="7" t="s">
-        <v>427</v>
-      </c>
       <c r="K80" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="Q80" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="R80" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S80" s="1">
         <v>1</v>
-      </c>
-      <c r="T80" s="1" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.3">
@@ -6131,40 +6059,40 @@
         <v>79</v>
       </c>
       <c r="B81" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>5</v>
+        <v>425</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="R81" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S81" s="1">
         <v>0</v>
@@ -6175,40 +6103,40 @@
         <v>80</v>
       </c>
       <c r="B82" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C82" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="G82" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="D82" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E82" s="8" t="s">
+      <c r="H82" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="F82" s="8" t="s">
+      <c r="I82" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J82" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="G82" s="8" t="s">
-        <v>435</v>
-      </c>
-      <c r="H82" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="I82" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J82" s="7" t="s">
-        <v>437</v>
-      </c>
       <c r="K82" s="2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="R82" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S82" s="1">
         <v>0</v>
@@ -6219,40 +6147,43 @@
         <v>81</v>
       </c>
       <c r="B83" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="G83" s="8" t="s">
         <v>438</v>
       </c>
-      <c r="D83" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E83" s="8" t="s">
+      <c r="H83" s="8" t="s">
         <v>439</v>
       </c>
-      <c r="F83" s="8" t="s">
+      <c r="I83" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="J83" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="G83" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="H83" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="I83" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="J83" s="7" t="s">
-        <v>443</v>
-      </c>
       <c r="K83" s="2" t="s">
-        <v>620</v>
+        <v>617</v>
+      </c>
+      <c r="Q83" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="R83" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S83" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.3">
@@ -6260,40 +6191,40 @@
         <v>82</v>
       </c>
       <c r="B84" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="H84" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="D84" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E84" s="8" t="s">
+      <c r="I84" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="F84" s="8" t="s">
+      <c r="J84" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="G84" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="H84" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="I84" s="8" t="s">
-        <v>448</v>
-      </c>
-      <c r="J84" s="7" t="s">
-        <v>449</v>
-      </c>
       <c r="K84" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="R84" s="1">
         <v>0</v>
       </c>
       <c r="S84" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.3">
@@ -6301,40 +6232,40 @@
         <v>83</v>
       </c>
       <c r="B85" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>5</v>
+        <v>447</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="R85" s="1">
         <v>0</v>
       </c>
       <c r="S85" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.3">
@@ -6342,40 +6273,40 @@
         <v>84</v>
       </c>
       <c r="B86" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>5</v>
+        <v>451</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="E86" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I86" s="8" t="s">
         <v>7</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="R86" s="1">
         <v>0</v>
       </c>
       <c r="S86" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.3">
@@ -6383,40 +6314,40 @@
         <v>85</v>
       </c>
       <c r="B87" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="G87" s="8" t="s">
         <v>458</v>
       </c>
-      <c r="D87" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E87" s="8" t="s">
+      <c r="H87" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="F87" s="8" t="s">
+      <c r="I87" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="J87" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="G87" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="H87" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="I87" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="J87" s="7" t="s">
-        <v>463</v>
-      </c>
       <c r="K87" s="2" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="R87" s="1">
         <v>0</v>
       </c>
       <c r="S87" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.3">
@@ -6424,40 +6355,43 @@
         <v>86</v>
       </c>
       <c r="B88" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>5</v>
+        <v>461</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="E88" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I88" s="8" t="s">
         <v>1</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>625</v>
+        <v>622</v>
+      </c>
+      <c r="Q88" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="R88" s="1">
         <v>0</v>
       </c>
       <c r="S88" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.3">
@@ -6465,40 +6399,43 @@
         <v>87</v>
       </c>
       <c r="B89" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>5</v>
+        <v>465</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="E89" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F89" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="H89" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="J89" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="G89" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="H89" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="I89" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="J89" s="7" t="s">
-        <v>472</v>
-      </c>
       <c r="K89" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
+      </c>
+      <c r="Q89" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="R89" s="1">
         <v>0</v>
       </c>
       <c r="S89" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.3">
@@ -6506,40 +6443,43 @@
         <v>88</v>
       </c>
       <c r="B90" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>5</v>
+        <v>470</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F90" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="H90" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="J90" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="G90" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="H90" s="8" t="s">
-        <v>475</v>
-      </c>
-      <c r="I90" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="J90" s="7" t="s">
-        <v>477</v>
-      </c>
       <c r="K90" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
+      </c>
+      <c r="Q90" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="R90" s="1">
         <v>0</v>
       </c>
       <c r="S90" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.3">
@@ -6547,40 +6487,43 @@
         <v>89</v>
       </c>
       <c r="B91" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>5</v>
+        <v>475</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="E91" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
+      </c>
+      <c r="Q91" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="R91" s="1">
         <v>0</v>
       </c>
       <c r="S91" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.3">
@@ -6588,40 +6531,43 @@
         <v>90</v>
       </c>
       <c r="B92" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>5</v>
+        <v>479</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="E92" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I92" s="8" t="s">
         <v>7</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>629</v>
+        <v>626</v>
+      </c>
+      <c r="Q92" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="R92" s="1">
         <v>0</v>
       </c>
       <c r="S92" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.3">
@@ -6629,40 +6575,43 @@
         <v>91</v>
       </c>
       <c r="B93" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C93" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="G93" s="8" t="s">
         <v>486</v>
       </c>
-      <c r="D93" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E93" s="8" t="s">
+      <c r="H93" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="F93" s="8" t="s">
+      <c r="I93" s="8" t="s">
         <v>488</v>
       </c>
-      <c r="G93" s="8" t="s">
+      <c r="J93" s="7" t="s">
         <v>489</v>
       </c>
-      <c r="H93" s="8" t="s">
-        <v>490</v>
-      </c>
-      <c r="I93" s="8" t="s">
-        <v>491</v>
-      </c>
-      <c r="J93" s="7" t="s">
-        <v>492</v>
-      </c>
       <c r="K93" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
+      </c>
+      <c r="Q93" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="R93" s="1">
         <v>0</v>
       </c>
       <c r="S93" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.3">
@@ -6670,40 +6619,43 @@
         <v>92</v>
       </c>
       <c r="B94" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>493</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>5</v>
+        <v>490</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="E94" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>631</v>
+        <v>628</v>
+      </c>
+      <c r="Q94" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="R94" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S94" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.3">
@@ -6711,40 +6663,43 @@
         <v>93</v>
       </c>
       <c r="B95" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C95" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="G95" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="D95" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E95" s="8" t="s">
+      <c r="H95" s="8" t="s">
         <v>498</v>
       </c>
-      <c r="F95" s="8" t="s">
+      <c r="I95" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J95" s="7" t="s">
         <v>499</v>
       </c>
-      <c r="G95" s="8" t="s">
-        <v>500</v>
-      </c>
-      <c r="H95" s="8" t="s">
-        <v>501</v>
-      </c>
-      <c r="I95" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J95" s="7" t="s">
-        <v>502</v>
-      </c>
       <c r="K95" s="2" t="s">
-        <v>632</v>
+        <v>629</v>
+      </c>
+      <c r="Q95" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="R95" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S95" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.3">
@@ -6752,40 +6707,43 @@
         <v>94</v>
       </c>
       <c r="B96" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>5</v>
+        <v>415</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="E96" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="H96" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J96" s="7" t="s">
         <v>503</v>
       </c>
-      <c r="F96" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="G96" s="8" t="s">
-        <v>504</v>
-      </c>
-      <c r="H96" s="8" t="s">
-        <v>505</v>
-      </c>
-      <c r="I96" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J96" s="7" t="s">
-        <v>506</v>
-      </c>
       <c r="K96" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
+      </c>
+      <c r="Q96" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="R96" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S96" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.3">
@@ -6793,40 +6751,43 @@
         <v>95</v>
       </c>
       <c r="B97" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C97" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="G97" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="D97" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E97" s="8" t="s">
+      <c r="H97" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="F97" s="8" t="s">
+      <c r="I97" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="J97" s="7" t="s">
         <v>509</v>
       </c>
-      <c r="G97" s="8" t="s">
-        <v>510</v>
-      </c>
-      <c r="H97" s="8" t="s">
-        <v>511</v>
-      </c>
-      <c r="I97" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="J97" s="7" t="s">
-        <v>512</v>
-      </c>
       <c r="K97" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
+      </c>
+      <c r="Q97" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="R97" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S97" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.3">
@@ -6834,40 +6795,43 @@
         <v>96</v>
       </c>
       <c r="B98" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C98" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="G98" s="8" t="s">
         <v>513</v>
       </c>
-      <c r="D98" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E98" s="8" t="s">
+      <c r="H98" s="8" t="s">
         <v>514</v>
       </c>
-      <c r="F98" s="8" t="s">
+      <c r="I98" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J98" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="G98" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="H98" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="I98" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J98" s="7" t="s">
-        <v>518</v>
-      </c>
       <c r="K98" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
+      </c>
+      <c r="Q98" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="R98" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S98" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.3">
@@ -6875,40 +6839,43 @@
         <v>97</v>
       </c>
       <c r="B99" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C99" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G99" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="D99" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E99" s="8" t="s">
+      <c r="H99" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="F99" s="8" t="s">
+      <c r="I99" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J99" s="7" t="s">
         <v>521</v>
       </c>
-      <c r="G99" s="8" t="s">
-        <v>522</v>
-      </c>
-      <c r="H99" s="8" t="s">
-        <v>523</v>
-      </c>
-      <c r="I99" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J99" s="7" t="s">
-        <v>524</v>
-      </c>
       <c r="K99" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
+      </c>
+      <c r="Q99" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="R99" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S99" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.3">
@@ -6916,40 +6883,43 @@
         <v>98</v>
       </c>
       <c r="B100" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C100" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="G100" s="8" t="s">
         <v>525</v>
       </c>
-      <c r="D100" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" s="8" t="s">
+      <c r="H100" s="8" t="s">
         <v>526</v>
       </c>
-      <c r="F100" s="8" t="s">
+      <c r="I100" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J100" s="7" t="s">
         <v>527</v>
       </c>
-      <c r="G100" s="8" t="s">
-        <v>528</v>
-      </c>
-      <c r="H100" s="8" t="s">
-        <v>529</v>
-      </c>
-      <c r="I100" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J100" s="7" t="s">
-        <v>530</v>
-      </c>
       <c r="K100" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
+      </c>
+      <c r="Q100" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="R100" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S100" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.3">
@@ -6957,40 +6927,43 @@
         <v>99</v>
       </c>
       <c r="B101" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>5</v>
+        <v>528</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="E101" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
+      </c>
+      <c r="Q101" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="R101" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S101" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.3">
@@ -6998,40 +6971,43 @@
         <v>100</v>
       </c>
       <c r="B102" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C102" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>533</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="G102" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="D102" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E102" s="8" t="s">
+      <c r="H102" s="8" t="s">
         <v>536</v>
       </c>
-      <c r="F102" s="8" t="s">
+      <c r="I102" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="J102" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="G102" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="H102" s="8" t="s">
-        <v>539</v>
-      </c>
-      <c r="I102" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="J102" s="7" t="s">
-        <v>540</v>
-      </c>
       <c r="K102" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
+      </c>
+      <c r="Q102" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="R102" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S102" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.3">

--- a/현황1.xlsx
+++ b/현황1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python\Python314\py_work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF966BE3-955C-4DE7-920C-EEA3665F55B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5305EF-F934-4B02-BF75-F69C0C9C2451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41640" yWindow="5880" windowWidth="31095" windowHeight="17145" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41265" yWindow="2685" windowWidth="31095" windowHeight="17145" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="맵핑" sheetId="3" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1882" uniqueCount="955">
   <si>
     <t>도소매 및 소비자용품수리업</t>
   </si>
@@ -405,9 +405,6 @@
     <t>대정천막산업</t>
   </si>
   <si>
-    <t>12581721410</t>
-  </si>
-  <si>
     <t>태흥정밀（주）</t>
   </si>
   <si>
@@ -2830,10 +2827,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>경기 화성시 만세구 장안면 금의솔안길 43-7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>경기 화성시 만세구 우정읍 쌍봉로 507-18</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3011,6 +3004,10 @@
   </si>
   <si>
     <t>기타식료품제조업</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>경기 화성시 만세구 장안면 금의솔안길 43-14</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3082,12 +3079,18 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -3121,7 +3124,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
@@ -3161,6 +3164,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4938,13 +4956,13 @@
         <v>10</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>8</v>
@@ -4953,16 +4971,16 @@
         <v>7</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>876</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>877</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>878</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>16</v>
@@ -5064,31 +5082,31 @@
         <v>37</v>
       </c>
       <c r="H3" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>928</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="K3" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="I3" s="10" t="s">
-        <v>930</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="K3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="L3" s="8" t="s">
-        <v>263</v>
-      </c>
       <c r="M3" s="9">
         <v>0</v>
       </c>
       <c r="N3" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="O3" s="9" t="s">
         <v>574</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="P3" s="9" t="s">
         <v>575</v>
-      </c>
-      <c r="P3" s="9" t="s">
-        <v>576</v>
       </c>
       <c r="X3" s="1">
         <v>0</v>
@@ -5117,31 +5135,31 @@
         <v>39</v>
       </c>
       <c r="H4" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>929</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="K4" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="I4" s="10" t="s">
-        <v>931</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="L4" s="8" t="s">
-        <v>266</v>
-      </c>
       <c r="M4" s="9" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="N4" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="O4" s="9" t="s">
         <v>577</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="P4" s="9" t="s">
         <v>578</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>579</v>
       </c>
       <c r="X4" s="1">
         <v>0</v>
@@ -5170,31 +5188,31 @@
         <v>41</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K5" s="8" t="s">
         <v>22</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N5" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="O5" s="9" t="s">
         <v>580</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="P5" s="9" t="s">
         <v>581</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>582</v>
       </c>
       <c r="X5" s="1">
         <v>0</v>
@@ -5223,31 +5241,31 @@
         <v>43</v>
       </c>
       <c r="H6" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>953</v>
+      </c>
+      <c r="L6" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="I6" s="10" t="s">
-        <v>933</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>955</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>270</v>
-      </c>
       <c r="M6" s="9">
         <v>0</v>
       </c>
       <c r="N6" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="O6" s="9" t="s">
         <v>583</v>
       </c>
-      <c r="O6" s="9" t="s">
+      <c r="P6" s="9" t="s">
         <v>584</v>
-      </c>
-      <c r="P6" s="9" t="s">
-        <v>585</v>
       </c>
       <c r="X6" s="1">
         <v>0</v>
@@ -5276,31 +5294,31 @@
         <v>45</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>21</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="N7" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="O7" s="9" t="s">
         <v>586</v>
       </c>
-      <c r="O7" s="9" t="s">
-        <v>587</v>
-      </c>
       <c r="P7" s="9" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="X7" s="1">
         <v>1</v>
@@ -5329,84 +5347,87 @@
         <v>47</v>
       </c>
       <c r="H8" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="K8" s="8" t="s">
         <v>273</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>274</v>
       </c>
       <c r="L8" s="8"/>
       <c r="M8" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="X8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="16">
+        <v>9</v>
+      </c>
+      <c r="B9" s="17">
+        <v>2</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="I9" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>462</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="L9" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="M9" s="20" t="s">
         <v>490</v>
       </c>
-      <c r="N8" s="9" t="s">
-        <v>588</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>589</v>
-      </c>
-      <c r="P8" s="9" t="s">
+      <c r="N9" s="20" t="s">
         <v>590</v>
       </c>
-      <c r="X8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="O9" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="P9" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="W9" s="17">
         <v>9</v>
       </c>
-      <c r="B9" s="1">
-        <v>2</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>463</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>491</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>591</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>592</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>593</v>
-      </c>
-      <c r="X9" s="1">
+      <c r="X9" s="17">
         <v>0</v>
       </c>
     </row>
@@ -5433,31 +5454,31 @@
         <v>51</v>
       </c>
       <c r="H10" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>952</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="I10" s="10" t="s">
-        <v>935</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>954</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>279</v>
-      </c>
       <c r="M10" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="N10" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="O10" s="9" t="s">
         <v>594</v>
       </c>
-      <c r="O10" s="9" t="s">
+      <c r="P10" s="9" t="s">
         <v>595</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>596</v>
       </c>
       <c r="X10" s="1">
         <v>1</v>
@@ -5486,31 +5507,31 @@
         <v>53</v>
       </c>
       <c r="H11" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="I11" s="10" t="s">
-        <v>936</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="K11" s="8" t="s">
+      <c r="L11" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="L11" s="8" t="s">
-        <v>282</v>
-      </c>
       <c r="M11" s="9" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N11" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="O11" s="9" t="s">
         <v>597</v>
       </c>
-      <c r="O11" s="9" t="s">
+      <c r="P11" s="9" t="s">
         <v>598</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>599</v>
       </c>
       <c r="X11" s="1">
         <v>0</v>
@@ -5539,31 +5560,31 @@
         <v>55</v>
       </c>
       <c r="H12" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="K12" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="I12" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>466</v>
-      </c>
-      <c r="K12" s="8" t="s">
+      <c r="L12" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="L12" s="8" t="s">
-        <v>285</v>
-      </c>
       <c r="M12" s="9" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N12" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="O12" s="9" t="s">
         <v>600</v>
       </c>
-      <c r="O12" s="9" t="s">
+      <c r="P12" s="9" t="s">
         <v>601</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>602</v>
       </c>
       <c r="X12" s="1">
         <v>1</v>
@@ -5592,31 +5613,31 @@
         <v>57</v>
       </c>
       <c r="H13" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="I13" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>467</v>
-      </c>
-      <c r="K13" s="8" t="s">
+      <c r="L13" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="L13" s="8" t="s">
-        <v>288</v>
-      </c>
       <c r="M13" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="N13" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="O13" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="O13" s="9" t="s">
-        <v>604</v>
-      </c>
       <c r="P13" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="X13" s="1">
         <v>0</v>
@@ -5645,31 +5666,31 @@
         <v>59</v>
       </c>
       <c r="H14" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="I14" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>463</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>290</v>
-      </c>
       <c r="M14" s="9">
         <v>0</v>
       </c>
       <c r="N14" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="O14" s="9" t="s">
         <v>605</v>
       </c>
-      <c r="O14" s="9" t="s">
-        <v>606</v>
-      </c>
       <c r="P14" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="X14" s="1">
         <v>0</v>
@@ -5698,31 +5719,31 @@
         <v>61</v>
       </c>
       <c r="H15" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="L15" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="I15" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>463</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>292</v>
-      </c>
       <c r="M15" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N15" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="O15" s="9" t="s">
         <v>607</v>
       </c>
-      <c r="O15" s="9" t="s">
-        <v>608</v>
-      </c>
       <c r="P15" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="X15" s="1">
         <v>0</v>
@@ -5751,31 +5772,31 @@
         <v>63</v>
       </c>
       <c r="H16" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="L16" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="I16" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>294</v>
-      </c>
       <c r="M16" s="9" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="N16" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="O16" s="9" t="s">
         <v>609</v>
       </c>
-      <c r="O16" s="9" t="s">
-        <v>610</v>
-      </c>
       <c r="P16" s="9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="X16" s="1">
         <v>0</v>
@@ -5804,31 +5825,31 @@
         <v>65</v>
       </c>
       <c r="H17" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="L17" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="I17" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>296</v>
-      </c>
       <c r="M17" s="9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="N17" s="9" t="s">
+        <v>610</v>
+      </c>
+      <c r="O17" s="9" t="s">
         <v>611</v>
       </c>
-      <c r="O17" s="9" t="s">
-        <v>612</v>
-      </c>
       <c r="P17" s="9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X17" s="1">
         <v>0</v>
@@ -5857,31 +5878,31 @@
         <v>67</v>
       </c>
       <c r="H18" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="K18" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="I18" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="K18" s="8" t="s">
+      <c r="L18" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="L18" s="8" t="s">
-        <v>299</v>
-      </c>
       <c r="M18" s="9" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="N18" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="O18" s="9" t="s">
         <v>613</v>
       </c>
-      <c r="O18" s="9" t="s">
+      <c r="P18" s="9" t="s">
         <v>614</v>
-      </c>
-      <c r="P18" s="9" t="s">
-        <v>615</v>
       </c>
       <c r="X18" s="1">
         <v>1</v>
@@ -5910,31 +5931,31 @@
         <v>69</v>
       </c>
       <c r="H19" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="L19" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="I19" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>301</v>
-      </c>
       <c r="M19" s="9" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="N19" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="O19" s="9" t="s">
         <v>616</v>
       </c>
-      <c r="O19" s="9" t="s">
+      <c r="P19" s="9" t="s">
         <v>617</v>
-      </c>
-      <c r="P19" s="9" t="s">
-        <v>618</v>
       </c>
       <c r="X19" s="1">
         <v>0</v>
@@ -5957,37 +5978,37 @@
         <v>1</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H20" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>935</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="L20" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="I20" s="10" t="s">
-        <v>937</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>303</v>
-      </c>
       <c r="M20" s="9" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="P20" s="9" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="X20" s="1">
         <v>2</v>
@@ -6016,31 +6037,31 @@
         <v>72</v>
       </c>
       <c r="H21" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="K21" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="I21" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="K21" s="8" t="s">
+      <c r="L21" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="L21" s="8" t="s">
-        <v>306</v>
-      </c>
       <c r="M21" s="9" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="X21" s="1">
         <v>0</v>
@@ -6069,31 +6090,31 @@
         <v>74</v>
       </c>
       <c r="H22" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>879</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="K22" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="I22" s="10" t="s">
-        <v>880</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="K22" s="8" t="s">
+      <c r="L22" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="L22" s="8" t="s">
-        <v>309</v>
-      </c>
       <c r="M22" s="9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="N22" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="O22" s="9" t="s">
         <v>621</v>
       </c>
-      <c r="O22" s="9" t="s">
+      <c r="P22" s="9" t="s">
         <v>622</v>
-      </c>
-      <c r="P22" s="9" t="s">
-        <v>623</v>
       </c>
       <c r="X22" s="1">
         <v>0</v>
@@ -6122,31 +6143,31 @@
         <v>76</v>
       </c>
       <c r="H23" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>881</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="K23" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="I23" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="K23" s="8" t="s">
+      <c r="L23" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="L23" s="8" t="s">
-        <v>312</v>
-      </c>
       <c r="M23" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="N23" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="O23" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="O23" s="9" t="s">
+      <c r="P23" s="9" t="s">
         <v>625</v>
-      </c>
-      <c r="P23" s="9" t="s">
-        <v>626</v>
       </c>
       <c r="X23" s="1">
         <v>0</v>
@@ -6175,31 +6196,31 @@
         <v>78</v>
       </c>
       <c r="H24" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>880</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="K24" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="I24" s="10" t="s">
-        <v>881</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>472</v>
-      </c>
-      <c r="K24" s="8" t="s">
+      <c r="L24" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="L24" s="8" t="s">
-        <v>315</v>
-      </c>
       <c r="M24" s="9" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="N24" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="O24" s="9" t="s">
         <v>627</v>
       </c>
-      <c r="O24" s="9" t="s">
+      <c r="P24" s="9" t="s">
         <v>628</v>
-      </c>
-      <c r="P24" s="9" t="s">
-        <v>629</v>
       </c>
       <c r="X24" s="1">
         <v>0</v>
@@ -6228,31 +6249,31 @@
         <v>80</v>
       </c>
       <c r="H25" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="L25" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="I25" s="10" t="s">
-        <v>938</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>317</v>
-      </c>
       <c r="M25" s="9">
         <v>0</v>
       </c>
       <c r="N25" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="O25" s="9" t="s">
         <v>630</v>
       </c>
-      <c r="O25" s="9" t="s">
+      <c r="P25" s="9" t="s">
         <v>631</v>
-      </c>
-      <c r="P25" s="9" t="s">
-        <v>632</v>
       </c>
       <c r="X25" s="1">
         <v>0</v>
@@ -6281,31 +6302,31 @@
         <v>82</v>
       </c>
       <c r="H26" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>937</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="L26" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="I26" s="10" t="s">
-        <v>939</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>319</v>
-      </c>
       <c r="M26" s="9">
         <v>0</v>
       </c>
       <c r="N26" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="O26" s="9" t="s">
         <v>633</v>
       </c>
-      <c r="O26" s="9" t="s">
+      <c r="P26" s="9" t="s">
         <v>634</v>
-      </c>
-      <c r="P26" s="9" t="s">
-        <v>635</v>
       </c>
       <c r="X26" s="1">
         <v>0</v>
@@ -6334,31 +6355,31 @@
         <v>84</v>
       </c>
       <c r="H27" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="L27" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="I27" s="10" t="s">
-        <v>940</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>321</v>
-      </c>
       <c r="M27" s="9" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="N27" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="O27" s="9" t="s">
         <v>636</v>
       </c>
-      <c r="O27" s="9" t="s">
+      <c r="P27" s="9" t="s">
         <v>637</v>
-      </c>
-      <c r="P27" s="9" t="s">
-        <v>638</v>
       </c>
       <c r="X27" s="1">
         <v>0</v>
@@ -6387,31 +6408,31 @@
         <v>86</v>
       </c>
       <c r="H28" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>939</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="K28" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="I28" s="10" t="s">
-        <v>941</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="K28" s="8" t="s">
+      <c r="L28" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="L28" s="8" t="s">
-        <v>324</v>
-      </c>
       <c r="M28" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="N28" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="O28" s="9" t="s">
         <v>639</v>
       </c>
-      <c r="O28" s="9" t="s">
+      <c r="P28" s="9" t="s">
         <v>640</v>
-      </c>
-      <c r="P28" s="9" t="s">
-        <v>641</v>
       </c>
       <c r="X28" s="1">
         <v>0</v>
@@ -6440,31 +6461,31 @@
         <v>88</v>
       </c>
       <c r="H29" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="K29" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="I29" s="10" t="s">
-        <v>883</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="K29" s="8" t="s">
+      <c r="L29" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="L29" s="8" t="s">
-        <v>327</v>
-      </c>
       <c r="M29" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="N29" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="O29" s="9" t="s">
         <v>642</v>
       </c>
-      <c r="O29" s="9" t="s">
+      <c r="P29" s="9" t="s">
         <v>643</v>
-      </c>
-      <c r="P29" s="9" t="s">
-        <v>644</v>
       </c>
       <c r="X29" s="1">
         <v>0</v>
@@ -6493,31 +6514,31 @@
         <v>90</v>
       </c>
       <c r="H30" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="L30" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="I30" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>467</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="L30" s="8" t="s">
-        <v>329</v>
-      </c>
       <c r="M30" s="9">
         <v>0</v>
       </c>
       <c r="N30" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="O30" s="9" t="s">
         <v>645</v>
       </c>
-      <c r="O30" s="9" t="s">
-        <v>646</v>
-      </c>
       <c r="P30" s="9" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="X30" s="1">
         <v>0</v>
@@ -6546,31 +6567,31 @@
         <v>92</v>
       </c>
       <c r="H31" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="L31" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="I31" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>467</v>
-      </c>
-      <c r="K31" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>331</v>
-      </c>
       <c r="M31" s="9" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="X31" s="1">
         <v>0</v>
@@ -6599,31 +6620,31 @@
         <v>94</v>
       </c>
       <c r="H32" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>940</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="L32" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="I32" s="10" t="s">
-        <v>942</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>463</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>333</v>
-      </c>
       <c r="M32" s="9">
         <v>0</v>
       </c>
       <c r="N32" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="O32" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="O32" s="9" t="s">
+      <c r="P32" s="9" t="s">
         <v>649</v>
-      </c>
-      <c r="P32" s="9" t="s">
-        <v>650</v>
       </c>
       <c r="X32" s="1">
         <v>1</v>
@@ -6652,29 +6673,29 @@
         <v>96</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L33" s="8"/>
       <c r="M33" s="9" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="N33" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="O33" s="9" t="s">
         <v>651</v>
       </c>
-      <c r="O33" s="9" t="s">
-        <v>652</v>
-      </c>
       <c r="P33" s="9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X33" s="1">
         <v>0</v>
@@ -6703,31 +6724,31 @@
         <v>98</v>
       </c>
       <c r="H34" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>884</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="L34" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="I34" s="10" t="s">
-        <v>885</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="L34" s="8" t="s">
-        <v>336</v>
-      </c>
       <c r="M34" s="9" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="N34" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="O34" s="9" t="s">
         <v>653</v>
       </c>
-      <c r="O34" s="9" t="s">
-        <v>654</v>
-      </c>
       <c r="P34" s="9" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="X34" s="1">
         <v>1</v>
@@ -6756,31 +6777,31 @@
         <v>100</v>
       </c>
       <c r="H35" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="L35" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="I35" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="L35" s="8" t="s">
-        <v>338</v>
-      </c>
       <c r="M35" s="9">
         <v>0</v>
       </c>
       <c r="N35" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="O35" s="9" t="s">
         <v>655</v>
       </c>
-      <c r="O35" s="9" t="s">
+      <c r="P35" s="9" t="s">
         <v>656</v>
-      </c>
-      <c r="P35" s="9" t="s">
-        <v>657</v>
       </c>
       <c r="X35" s="1">
         <v>0</v>
@@ -6809,31 +6830,31 @@
         <v>102</v>
       </c>
       <c r="H36" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>885</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="K36" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="I36" s="10" t="s">
-        <v>886</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>475</v>
-      </c>
-      <c r="K36" s="8" t="s">
+      <c r="L36" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="L36" s="8" t="s">
-        <v>341</v>
-      </c>
       <c r="M36" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="N36" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="O36" s="9" t="s">
         <v>658</v>
       </c>
-      <c r="O36" s="9" t="s">
-        <v>659</v>
-      </c>
       <c r="P36" s="9" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="X36" s="1">
         <v>0</v>
@@ -6862,31 +6883,31 @@
         <v>104</v>
       </c>
       <c r="H37" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="K37" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="I37" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="J37" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="K37" s="8" t="s">
+      <c r="L37" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="L37" s="8" t="s">
-        <v>344</v>
-      </c>
       <c r="M37" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="N37" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="O37" s="9" t="s">
         <v>660</v>
       </c>
-      <c r="O37" s="9" t="s">
-        <v>661</v>
-      </c>
       <c r="P37" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="X37" s="1">
         <v>0</v>
@@ -6915,31 +6936,31 @@
         <v>106</v>
       </c>
       <c r="H38" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="L38" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="I38" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="K38" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="L38" s="8" t="s">
-        <v>346</v>
-      </c>
       <c r="M38" s="9">
         <v>0</v>
       </c>
       <c r="N38" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="O38" s="9" t="s">
         <v>662</v>
       </c>
-      <c r="O38" s="9" t="s">
-        <v>663</v>
-      </c>
       <c r="P38" s="9" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="X38" s="1">
         <v>0</v>
@@ -6968,31 +6989,31 @@
         <v>108</v>
       </c>
       <c r="H39" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>941</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="L39" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="I39" s="10" t="s">
-        <v>943</v>
-      </c>
-      <c r="J39" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="K39" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="L39" s="8" t="s">
-        <v>348</v>
-      </c>
       <c r="M39" s="9" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="N39" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="O39" s="9" t="s">
         <v>664</v>
       </c>
-      <c r="O39" s="9" t="s">
-        <v>665</v>
-      </c>
       <c r="P39" s="9" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="X39" s="1">
         <v>0</v>
@@ -7021,31 +7042,31 @@
         <v>110</v>
       </c>
       <c r="H40" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="K40" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="I40" s="10" t="s">
-        <v>944</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="K40" s="8" t="s">
+      <c r="L40" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="L40" s="8" t="s">
-        <v>351</v>
-      </c>
       <c r="M40" s="9" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="N40" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="O40" s="9" t="s">
         <v>666</v>
       </c>
-      <c r="O40" s="9" t="s">
-        <v>667</v>
-      </c>
       <c r="P40" s="9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="X40" s="1">
         <v>0</v>
@@ -7074,31 +7095,31 @@
         <v>112</v>
       </c>
       <c r="H41" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>944</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="L41" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="I41" s="10" t="s">
-        <v>946</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>463</v>
-      </c>
-      <c r="K41" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="L41" s="8" t="s">
-        <v>353</v>
-      </c>
       <c r="M41" s="9">
         <v>0</v>
       </c>
       <c r="N41" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="O41" s="9" t="s">
         <v>668</v>
       </c>
-      <c r="O41" s="9" t="s">
-        <v>669</v>
-      </c>
       <c r="P41" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="X41" s="1">
         <v>0</v>
@@ -7127,86 +7148,89 @@
         <v>114</v>
       </c>
       <c r="H42" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="L42" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="I42" s="10" t="s">
+      <c r="M42" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="N42" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="O42" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="P42" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="X42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="16">
+        <v>43</v>
+      </c>
+      <c r="B43" s="17">
+        <v>2</v>
+      </c>
+      <c r="C43" s="18">
+        <v>12581721410</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E43" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="G43" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="H43" s="18" t="s">
+        <v>355</v>
+      </c>
+      <c r="I43" s="19" t="s">
         <v>945</v>
       </c>
-      <c r="J42" s="8" t="s">
-        <v>467</v>
-      </c>
-      <c r="K42" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="L42" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="M42" s="9" t="s">
+      <c r="J43" s="18" t="s">
+        <v>470</v>
+      </c>
+      <c r="K43" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="L43" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="M43" s="20" t="s">
         <v>516</v>
       </c>
-      <c r="N42" s="9" t="s">
-        <v>670</v>
-      </c>
-      <c r="O42" s="9" t="s">
+      <c r="N43" s="20" t="s">
+        <v>612</v>
+      </c>
+      <c r="O43" s="20" t="s">
+        <v>672</v>
+      </c>
+      <c r="P43" s="20" t="s">
         <v>671</v>
       </c>
-      <c r="P42" s="9" t="s">
-        <v>672</v>
-      </c>
-      <c r="X42" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
-        <v>43</v>
-      </c>
-      <c r="B43" s="1">
-        <v>2</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>947</v>
-      </c>
-      <c r="J43" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="K43" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="L43" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="M43" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="N43" s="9" t="s">
-        <v>613</v>
-      </c>
-      <c r="O43" s="9" t="s">
-        <v>673</v>
-      </c>
-      <c r="P43" s="9" t="s">
-        <v>672</v>
-      </c>
-      <c r="X43" s="1">
+      <c r="W43" s="17">
+        <v>9</v>
+      </c>
+      <c r="X43" s="17">
         <v>0</v>
       </c>
     </row>
@@ -7218,46 +7242,46 @@
         <v>2</v>
       </c>
       <c r="C44" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="D44" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>118</v>
-      </c>
       <c r="G44" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H44" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="L44" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="I44" s="10" t="s">
-        <v>948</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="K44" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="L44" s="8" t="s">
-        <v>359</v>
-      </c>
       <c r="M44" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="N44" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="O44" s="9" t="s">
         <v>674</v>
       </c>
-      <c r="O44" s="9" t="s">
-        <v>675</v>
-      </c>
       <c r="P44" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="X44" s="1">
         <v>0</v>
@@ -7271,46 +7295,46 @@
         <v>2</v>
       </c>
       <c r="C45" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="D45" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>120</v>
-      </c>
       <c r="G45" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H45" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="L45" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="I45" s="10" t="s">
-        <v>949</v>
-      </c>
-      <c r="J45" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="K45" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="L45" s="8" t="s">
-        <v>361</v>
-      </c>
       <c r="M45" s="9" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="N45" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="O45" s="9" t="s">
         <v>676</v>
       </c>
-      <c r="O45" s="9" t="s">
-        <v>677</v>
-      </c>
       <c r="P45" s="9" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="X45" s="1">
         <v>0</v>
@@ -7324,46 +7348,46 @@
         <v>1</v>
       </c>
       <c r="C46" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D46" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>122</v>
-      </c>
       <c r="G46" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H46" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="L46" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="I46" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="K46" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="L46" s="8" t="s">
-        <v>363</v>
-      </c>
       <c r="M46" s="9">
         <v>0</v>
       </c>
       <c r="N46" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="O46" s="9" t="s">
         <v>678</v>
       </c>
-      <c r="O46" s="9" t="s">
+      <c r="P46" s="9" t="s">
         <v>679</v>
-      </c>
-      <c r="P46" s="9" t="s">
-        <v>680</v>
       </c>
       <c r="X46" s="1">
         <v>0</v>
@@ -7377,46 +7401,46 @@
         <v>2</v>
       </c>
       <c r="C47" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="D47" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>124</v>
-      </c>
       <c r="G47" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H47" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>948</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="L47" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="I47" s="10" t="s">
-        <v>950</v>
-      </c>
-      <c r="J47" s="8" t="s">
-        <v>463</v>
-      </c>
-      <c r="K47" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="L47" s="8" t="s">
-        <v>365</v>
-      </c>
       <c r="M47" s="9" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="N47" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="O47" s="9" t="s">
         <v>681</v>
       </c>
-      <c r="O47" s="9" t="s">
-        <v>682</v>
-      </c>
       <c r="P47" s="9" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="X47" s="1">
         <v>0</v>
@@ -7430,46 +7454,46 @@
         <v>2</v>
       </c>
       <c r="C48" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="D48" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>126</v>
-      </c>
       <c r="G48" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H48" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>886</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="L48" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="I48" s="10" t="s">
-        <v>887</v>
-      </c>
-      <c r="J48" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="K48" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="L48" s="8" t="s">
-        <v>367</v>
-      </c>
       <c r="M48" s="9" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="N48" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="O48" s="9" t="s">
         <v>683</v>
       </c>
-      <c r="O48" s="9" t="s">
-        <v>684</v>
-      </c>
       <c r="P48" s="9" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="X48" s="1">
         <v>0</v>
@@ -7483,46 +7507,46 @@
         <v>2</v>
       </c>
       <c r="C49" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="D49" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>128</v>
-      </c>
       <c r="G49" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H49" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="L49" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="I49" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="J49" s="8" t="s">
-        <v>463</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="L49" s="8" t="s">
-        <v>369</v>
-      </c>
       <c r="M49" s="9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N49" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="O49" s="9" t="s">
         <v>685</v>
       </c>
-      <c r="O49" s="9" t="s">
+      <c r="P49" s="9" t="s">
         <v>686</v>
-      </c>
-      <c r="P49" s="9" t="s">
-        <v>687</v>
       </c>
       <c r="X49" s="1">
         <v>1</v>
@@ -7536,46 +7560,46 @@
         <v>2</v>
       </c>
       <c r="C50" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D50" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>130</v>
-      </c>
       <c r="G50" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H50" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="K50" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="I50" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="J50" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="K50" s="8" t="s">
+      <c r="L50" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="L50" s="8" t="s">
-        <v>372</v>
-      </c>
       <c r="M50" s="9" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="N50" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="O50" s="9" t="s">
         <v>688</v>
       </c>
-      <c r="O50" s="9" t="s">
-        <v>689</v>
-      </c>
       <c r="P50" s="9" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="X50" s="1">
         <v>0</v>
@@ -7589,46 +7613,46 @@
         <v>2</v>
       </c>
       <c r="C51" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F51" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D51" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>132</v>
-      </c>
       <c r="G51" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H51" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>478</v>
+      </c>
+      <c r="K51" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="I51" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="J51" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="K51" s="8" t="s">
+      <c r="L51" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="L51" s="8" t="s">
-        <v>375</v>
-      </c>
       <c r="M51" s="9" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="N51" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="O51" s="9" t="s">
         <v>690</v>
       </c>
-      <c r="O51" s="9" t="s">
-        <v>691</v>
-      </c>
       <c r="P51" s="9" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="X51" s="1">
         <v>0</v>
@@ -7642,46 +7666,46 @@
         <v>1</v>
       </c>
       <c r="C52" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D52" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>134</v>
-      </c>
       <c r="G52" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K52" s="8" t="s">
         <v>23</v>
       </c>
       <c r="L52" s="8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M52" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="N52" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="O52" s="9" t="s">
         <v>692</v>
       </c>
-      <c r="O52" s="9" t="s">
+      <c r="P52" s="9" t="s">
         <v>693</v>
-      </c>
-      <c r="P52" s="9" t="s">
-        <v>694</v>
       </c>
       <c r="X52" s="1">
         <v>0</v>
@@ -7695,46 +7719,46 @@
         <v>2</v>
       </c>
       <c r="C53" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D53" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>136</v>
-      </c>
       <c r="G53" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H53" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="K53" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="L53" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="I53" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="J53" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="K53" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="L53" s="8" t="s">
-        <v>379</v>
-      </c>
       <c r="M53" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="N53" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="O53" s="9" t="s">
         <v>695</v>
       </c>
-      <c r="O53" s="9" t="s">
-        <v>696</v>
-      </c>
       <c r="P53" s="9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X53" s="1">
         <v>0</v>
@@ -7748,28 +7772,28 @@
         <v>1</v>
       </c>
       <c r="C54" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="D54" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>138</v>
-      </c>
       <c r="G54" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K54" s="8" t="s">
         <v>0</v>
@@ -7779,13 +7803,13 @@
         <v>0</v>
       </c>
       <c r="N54" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="O54" s="9" t="s">
         <v>697</v>
       </c>
-      <c r="O54" s="9" t="s">
-        <v>698</v>
-      </c>
       <c r="P54" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="X54" s="1">
         <v>1</v>
@@ -7799,46 +7823,46 @@
         <v>2</v>
       </c>
       <c r="C55" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F55" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="D55" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>140</v>
-      </c>
       <c r="G55" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H55" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="I55" s="10" t="s">
+        <v>887</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="L55" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="I55" s="10" t="s">
-        <v>888</v>
-      </c>
-      <c r="J55" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="K55" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="L55" s="8" t="s">
-        <v>382</v>
-      </c>
       <c r="M55" s="9">
         <v>0</v>
       </c>
       <c r="N55" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="O55" s="9" t="s">
         <v>699</v>
       </c>
-      <c r="O55" s="9" t="s">
-        <v>700</v>
-      </c>
       <c r="P55" s="9" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="X55" s="1">
         <v>0</v>
@@ -7852,46 +7876,46 @@
         <v>2</v>
       </c>
       <c r="C56" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F56" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="D56" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>142</v>
-      </c>
       <c r="G56" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H56" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>949</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="L56" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="I56" s="10" t="s">
-        <v>951</v>
-      </c>
-      <c r="J56" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="K56" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="L56" s="8" t="s">
-        <v>384</v>
-      </c>
       <c r="M56" s="9">
         <v>0</v>
       </c>
       <c r="N56" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="O56" s="9" t="s">
         <v>701</v>
       </c>
-      <c r="O56" s="9" t="s">
-        <v>702</v>
-      </c>
       <c r="P56" s="9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X56" s="1">
         <v>0</v>
@@ -7905,46 +7929,46 @@
         <v>2</v>
       </c>
       <c r="C57" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F57" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D57" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>144</v>
-      </c>
       <c r="G57" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H57" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="K57" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="L57" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="I57" s="8" t="s">
+      <c r="M57" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="J57" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="K57" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="L57" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="M57" s="9" t="s">
-        <v>386</v>
-      </c>
       <c r="N57" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="O57" s="9" t="s">
         <v>703</v>
       </c>
-      <c r="O57" s="9" t="s">
-        <v>704</v>
-      </c>
       <c r="P57" s="9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X57" s="1">
         <v>0</v>
@@ -7958,46 +7982,46 @@
         <v>2</v>
       </c>
       <c r="C58" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D58" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>146</v>
-      </c>
       <c r="G58" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H58" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="L58" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="I58" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="J58" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="K58" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="L58" s="8" t="s">
-        <v>388</v>
-      </c>
       <c r="M58" s="9" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N58" s="9" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="O58" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="P58" s="9" t="s">
         <v>705</v>
-      </c>
-      <c r="P58" s="9" t="s">
-        <v>706</v>
       </c>
       <c r="X58" s="1">
         <v>0</v>
@@ -8011,46 +8035,46 @@
         <v>2</v>
       </c>
       <c r="C59" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F59" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="D59" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>148</v>
-      </c>
       <c r="G59" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H59" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="I59" s="10" t="s">
+        <v>917</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="K59" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="L59" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="I59" s="10" t="s">
-        <v>919</v>
-      </c>
-      <c r="J59" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="K59" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="L59" s="8" t="s">
-        <v>390</v>
-      </c>
       <c r="M59" s="9">
         <v>0</v>
       </c>
       <c r="N59" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="O59" s="9" t="s">
         <v>707</v>
       </c>
-      <c r="O59" s="9" t="s">
-        <v>708</v>
-      </c>
       <c r="P59" s="9" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="X59" s="1">
         <v>0</v>
@@ -8064,46 +8088,46 @@
         <v>2</v>
       </c>
       <c r="C60" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F60" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D60" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>150</v>
-      </c>
       <c r="G60" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H60" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="K60" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="L60" s="8" t="s">
         <v>391</v>
       </c>
-      <c r="I60" s="10" t="s">
-        <v>952</v>
-      </c>
-      <c r="J60" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="K60" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="L60" s="8" t="s">
-        <v>392</v>
-      </c>
       <c r="M60" s="9" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="N60" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="O60" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="O60" s="9" t="s">
-        <v>710</v>
-      </c>
       <c r="P60" s="9" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="X60" s="1">
         <v>0</v>
@@ -8117,46 +8141,46 @@
         <v>1</v>
       </c>
       <c r="C61" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="D61" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>152</v>
-      </c>
       <c r="G61" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H61" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="K61" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="L61" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="I61" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="J61" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="K61" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="L61" s="8" t="s">
-        <v>394</v>
-      </c>
       <c r="M61" s="9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N61" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="O61" s="9" t="s">
         <v>711</v>
       </c>
-      <c r="O61" s="9" t="s">
-        <v>712</v>
-      </c>
       <c r="P61" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="X61" s="1">
         <v>2</v>
@@ -8170,46 +8194,46 @@
         <v>1</v>
       </c>
       <c r="C62" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F62" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="D62" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>154</v>
-      </c>
       <c r="G62" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H62" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="I62" s="10" t="s">
+        <v>918</v>
+      </c>
+      <c r="J62" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="K62" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="L62" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="I62" s="10" t="s">
-        <v>920</v>
-      </c>
-      <c r="J62" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="K62" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="L62" s="8" t="s">
-        <v>396</v>
-      </c>
       <c r="M62" s="9">
         <v>0</v>
       </c>
       <c r="N62" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="O62" s="9" t="s">
         <v>713</v>
       </c>
-      <c r="O62" s="9" t="s">
+      <c r="P62" s="9" t="s">
         <v>714</v>
-      </c>
-      <c r="P62" s="9" t="s">
-        <v>715</v>
       </c>
       <c r="X62" s="1">
         <v>0</v>
@@ -8223,46 +8247,46 @@
         <v>2</v>
       </c>
       <c r="C63" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F63" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D63" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>156</v>
-      </c>
       <c r="G63" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H63" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="I63" s="10" t="s">
+        <v>919</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="K63" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="L63" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="I63" s="10" t="s">
-        <v>921</v>
-      </c>
-      <c r="J63" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="K63" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="L63" s="8" t="s">
-        <v>398</v>
-      </c>
       <c r="M63" s="9" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="N63" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="O63" s="9" t="s">
         <v>716</v>
       </c>
-      <c r="O63" s="9" t="s">
+      <c r="P63" s="9" t="s">
         <v>717</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>718</v>
       </c>
       <c r="X63" s="1">
         <v>0</v>
@@ -8276,46 +8300,46 @@
         <v>2</v>
       </c>
       <c r="C64" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D64" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>158</v>
-      </c>
       <c r="G64" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H64" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="I64" s="10" t="s">
+        <v>920</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="L64" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="I64" s="10" t="s">
-        <v>922</v>
-      </c>
-      <c r="J64" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="K64" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="L64" s="8" t="s">
-        <v>400</v>
-      </c>
       <c r="M64" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N64" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="O64" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="O64" s="9" t="s">
-        <v>720</v>
-      </c>
       <c r="P64" s="9" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="X64" s="1">
         <v>0</v>
@@ -8329,44 +8353,44 @@
         <v>1</v>
       </c>
       <c r="C65" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F65" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="D65" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>160</v>
-      </c>
       <c r="G65" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K65" s="8" t="s">
         <v>0</v>
       </c>
       <c r="L65" s="8"/>
       <c r="M65" s="9" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="N65" s="9" t="s">
+        <v>720</v>
+      </c>
+      <c r="O65" s="9" t="s">
         <v>721</v>
       </c>
-      <c r="O65" s="9" t="s">
+      <c r="P65" s="9" t="s">
         <v>722</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>723</v>
       </c>
       <c r="X65" s="1">
         <v>0</v>
@@ -8380,46 +8404,46 @@
         <v>2</v>
       </c>
       <c r="C66" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F66" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="D66" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>162</v>
-      </c>
       <c r="G66" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H66" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="I66" s="10" t="s">
+        <v>951</v>
+      </c>
+      <c r="J66" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="K66" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="L66" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="I66" s="10" t="s">
-        <v>953</v>
-      </c>
-      <c r="J66" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="K66" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="L66" s="8" t="s">
-        <v>403</v>
-      </c>
       <c r="M66" s="9" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="N66" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="O66" s="9" t="s">
         <v>724</v>
       </c>
-      <c r="O66" s="9" t="s">
-        <v>725</v>
-      </c>
       <c r="P66" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="X66" s="1">
         <v>0</v>
@@ -8433,46 +8457,46 @@
         <v>2</v>
       </c>
       <c r="C67" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F67" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D67" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>164</v>
-      </c>
       <c r="G67" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="J67" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K67" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="L67" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="L67" s="8" t="s">
-        <v>405</v>
-      </c>
       <c r="M67" s="9" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="X67" s="1">
         <v>0</v>
@@ -8486,46 +8510,46 @@
         <v>2</v>
       </c>
       <c r="C68" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F68" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="D68" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>166</v>
-      </c>
       <c r="G68" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K68" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L68" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="M68" s="9" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="N68" s="9" t="s">
+        <v>726</v>
+      </c>
+      <c r="O68" s="9" t="s">
         <v>727</v>
       </c>
-      <c r="O68" s="9" t="s">
-        <v>728</v>
-      </c>
       <c r="P68" s="9" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="X68" s="1">
         <v>0</v>
@@ -8539,46 +8563,46 @@
         <v>1</v>
       </c>
       <c r="C69" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F69" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="D69" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>168</v>
-      </c>
       <c r="G69" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K69" s="8" t="s">
         <v>0</v>
       </c>
       <c r="L69" s="8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="M69" s="9" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="N69" s="9" t="s">
+        <v>728</v>
+      </c>
+      <c r="O69" s="9" t="s">
         <v>729</v>
       </c>
-      <c r="O69" s="9" t="s">
-        <v>730</v>
-      </c>
       <c r="P69" s="9" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="X69" s="1">
         <v>0</v>
@@ -8592,46 +8616,46 @@
         <v>2</v>
       </c>
       <c r="C70" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F70" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="D70" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>170</v>
-      </c>
       <c r="G70" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K70" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L70" s="8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="M70" s="9" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="N70" s="9" t="s">
+        <v>730</v>
+      </c>
+      <c r="O70" s="9" t="s">
         <v>731</v>
       </c>
-      <c r="O70" s="9" t="s">
-        <v>732</v>
-      </c>
       <c r="P70" s="9" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="X70" s="1">
         <v>0</v>
@@ -8645,46 +8669,46 @@
         <v>2</v>
       </c>
       <c r="C71" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F71" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="D71" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>172</v>
-      </c>
       <c r="G71" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K71" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="L71" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="L71" s="8" t="s">
-        <v>299</v>
-      </c>
       <c r="M71" s="9" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="N71" s="9" t="s">
+        <v>732</v>
+      </c>
+      <c r="O71" s="9" t="s">
         <v>733</v>
       </c>
-      <c r="O71" s="9" t="s">
-        <v>734</v>
-      </c>
       <c r="P71" s="9" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="X71" s="1">
         <v>0</v>
@@ -8698,46 +8722,46 @@
         <v>2</v>
       </c>
       <c r="C72" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F72" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D72" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>174</v>
-      </c>
       <c r="G72" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K72" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L72" s="8" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="M72" s="9" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="N72" s="9" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="O72" s="9" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="P72" s="9" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="X72" s="1">
         <v>0</v>
@@ -8751,46 +8775,46 @@
         <v>2</v>
       </c>
       <c r="C73" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F73" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="D73" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>176</v>
-      </c>
       <c r="G73" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K73" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L73" s="8" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M73" s="9" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="N73" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="O73" s="9" t="s">
         <v>736</v>
       </c>
-      <c r="O73" s="9" t="s">
-        <v>737</v>
-      </c>
       <c r="P73" s="9" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="X73" s="1">
         <v>0</v>
@@ -8804,46 +8828,46 @@
         <v>2</v>
       </c>
       <c r="C74" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F74" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="D74" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>178</v>
-      </c>
       <c r="G74" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K74" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L74" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M74" s="9" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="N74" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="O74" s="9" t="s">
         <v>738</v>
       </c>
-      <c r="O74" s="9" t="s">
-        <v>739</v>
-      </c>
       <c r="P74" s="9" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="X74" s="1">
         <v>0</v>
@@ -8857,46 +8881,46 @@
         <v>2</v>
       </c>
       <c r="C75" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F75" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D75" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>180</v>
-      </c>
       <c r="G75" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K75" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L75" s="8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M75" s="9">
         <v>0</v>
       </c>
       <c r="N75" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="O75" s="9" t="s">
         <v>740</v>
       </c>
-      <c r="O75" s="9" t="s">
-        <v>741</v>
-      </c>
       <c r="P75" s="9" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="X75" s="1">
         <v>1</v>
@@ -8910,46 +8934,46 @@
         <v>2</v>
       </c>
       <c r="C76" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D76" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>182</v>
-      </c>
       <c r="G76" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K76" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L76" s="8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="M76" s="9" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="N76" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="O76" s="9" t="s">
         <v>742</v>
       </c>
-      <c r="O76" s="9" t="s">
-        <v>743</v>
-      </c>
       <c r="P76" s="9" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="X76" s="1">
         <v>0</v>
@@ -8963,46 +8987,46 @@
         <v>2</v>
       </c>
       <c r="C77" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F77" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D77" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>184</v>
-      </c>
       <c r="G77" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="J77" s="8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K77" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="L77" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="L77" s="8" t="s">
-        <v>415</v>
-      </c>
       <c r="M77" s="9">
         <v>0</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="X77" s="1">
         <v>0</v>
@@ -9016,46 +9040,46 @@
         <v>2</v>
       </c>
       <c r="C78" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F78" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D78" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>186</v>
-      </c>
       <c r="G78" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="J78" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K78" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L78" s="8" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="M78" s="9">
         <v>0</v>
       </c>
       <c r="N78" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="O78" s="9" t="s">
         <v>745</v>
       </c>
-      <c r="O78" s="9" t="s">
-        <v>746</v>
-      </c>
       <c r="P78" s="9" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="X78" s="1">
         <v>0</v>
@@ -9069,46 +9093,46 @@
         <v>2</v>
       </c>
       <c r="C79" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F79" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="D79" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>188</v>
-      </c>
       <c r="G79" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="J79" s="8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K79" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="L79" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="L79" s="8" t="s">
-        <v>418</v>
-      </c>
       <c r="M79" s="9" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="N79" s="9" t="s">
+        <v>746</v>
+      </c>
+      <c r="O79" s="9" t="s">
         <v>747</v>
       </c>
-      <c r="O79" s="9" t="s">
-        <v>748</v>
-      </c>
       <c r="P79" s="9" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="X79" s="1">
         <v>0</v>
@@ -9122,46 +9146,46 @@
         <v>2</v>
       </c>
       <c r="C80" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F80" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="D80" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>190</v>
-      </c>
       <c r="G80" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="J80" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K80" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L80" s="8" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M80" s="9" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="N80" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="O80" s="9" t="s">
         <v>749</v>
       </c>
-      <c r="O80" s="9" t="s">
-        <v>750</v>
-      </c>
       <c r="P80" s="9" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="X80" s="1">
         <v>0</v>
@@ -9175,46 +9199,46 @@
         <v>1</v>
       </c>
       <c r="C81" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F81" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="D81" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>192</v>
-      </c>
       <c r="G81" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="J81" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K81" s="8" t="s">
         <v>0</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="M81" s="9">
         <v>0</v>
       </c>
       <c r="N81" s="9" t="s">
+        <v>750</v>
+      </c>
+      <c r="O81" s="9" t="s">
         <v>751</v>
       </c>
-      <c r="O81" s="9" t="s">
+      <c r="P81" s="9" t="s">
         <v>752</v>
-      </c>
-      <c r="P81" s="9" t="s">
-        <v>753</v>
       </c>
       <c r="X81" s="1">
         <v>0</v>
@@ -9228,46 +9252,46 @@
         <v>2</v>
       </c>
       <c r="C82" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F82" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="D82" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>194</v>
-      </c>
       <c r="G82" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="J82" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="K82" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L82" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="M82" s="9" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="N82" s="9" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="O82" s="9" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="P82" s="9" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="X82" s="1">
         <v>1</v>
@@ -9281,46 +9305,46 @@
         <v>2</v>
       </c>
       <c r="C83" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F83" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D83" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F83" s="8" t="s">
-        <v>196</v>
-      </c>
       <c r="G83" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="J83" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K83" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L83" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M83" s="9" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O83" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="P83" s="9" t="s">
         <v>755</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>756</v>
       </c>
       <c r="X83" s="1">
         <v>0</v>
@@ -9334,46 +9358,46 @@
         <v>2</v>
       </c>
       <c r="C84" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F84" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="D84" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E84" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>198</v>
-      </c>
       <c r="G84" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K84" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L84" s="8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="M84" s="9" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="N84" s="9" t="s">
+        <v>756</v>
+      </c>
+      <c r="O84" s="9" t="s">
         <v>757</v>
       </c>
-      <c r="O84" s="9" t="s">
-        <v>758</v>
-      </c>
       <c r="P84" s="9" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="X84" s="1">
         <v>0</v>
@@ -9387,46 +9411,46 @@
         <v>2</v>
       </c>
       <c r="C85" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F85" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="D85" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>200</v>
-      </c>
       <c r="G85" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="J85" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K85" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="M85" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="N85" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="O85" s="9" t="s">
         <v>759</v>
       </c>
-      <c r="O85" s="9" t="s">
-        <v>760</v>
-      </c>
       <c r="P85" s="9" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="X85" s="1">
         <v>0</v>
@@ -9440,46 +9464,46 @@
         <v>1</v>
       </c>
       <c r="C86" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F86" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="D86" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E86" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F86" s="8" t="s">
-        <v>202</v>
-      </c>
       <c r="G86" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="J86" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K86" s="8" t="s">
         <v>0</v>
       </c>
       <c r="L86" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="M86" s="9" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N86" s="9" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="O86" s="9" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P86" s="9" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="X86" s="1">
         <v>1</v>
@@ -9493,46 +9517,46 @@
         <v>2</v>
       </c>
       <c r="C87" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F87" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="D87" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E87" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F87" s="8" t="s">
-        <v>204</v>
-      </c>
       <c r="G87" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="J87" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K87" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L87" s="8" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="M87" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="N87" s="9" t="s">
+        <v>761</v>
+      </c>
+      <c r="O87" s="9" t="s">
         <v>762</v>
       </c>
-      <c r="O87" s="9" t="s">
-        <v>763</v>
-      </c>
       <c r="P87" s="9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X87" s="1">
         <v>0</v>
@@ -9546,46 +9570,46 @@
         <v>2</v>
       </c>
       <c r="C88" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F88" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="D88" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F88" s="8" t="s">
-        <v>206</v>
-      </c>
       <c r="G88" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="J88" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K88" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L88" s="8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="M88" s="9" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="N88" s="9" t="s">
+        <v>763</v>
+      </c>
+      <c r="O88" s="9" t="s">
         <v>764</v>
       </c>
-      <c r="O88" s="9" t="s">
-        <v>765</v>
-      </c>
       <c r="P88" s="9" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="X88" s="1">
         <v>0</v>
@@ -9599,46 +9623,46 @@
         <v>2</v>
       </c>
       <c r="C89" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F89" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="D89" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F89" s="8" t="s">
-        <v>208</v>
-      </c>
       <c r="G89" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="J89" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K89" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L89" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M89" s="9" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="N89" s="9" t="s">
+        <v>765</v>
+      </c>
+      <c r="O89" s="9" t="s">
         <v>766</v>
       </c>
-      <c r="O89" s="9" t="s">
-        <v>767</v>
-      </c>
       <c r="P89" s="9" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="X89" s="1">
         <v>0</v>
@@ -9652,44 +9676,44 @@
         <v>2</v>
       </c>
       <c r="C90" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F90" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="D90" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E90" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F90" s="8" t="s">
-        <v>210</v>
-      </c>
       <c r="G90" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="J90" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K90" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L90" s="8"/>
       <c r="M90" s="9" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="N90" s="9" t="s">
+        <v>767</v>
+      </c>
+      <c r="O90" s="9" t="s">
         <v>768</v>
       </c>
-      <c r="O90" s="9" t="s">
-        <v>769</v>
-      </c>
       <c r="P90" s="9" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="X90" s="1">
         <v>0</v>
@@ -9703,46 +9727,46 @@
         <v>2</v>
       </c>
       <c r="C91" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F91" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="D91" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F91" s="8" t="s">
-        <v>212</v>
-      </c>
       <c r="G91" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="J91" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K91" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="M91" s="9" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="N91" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="O91" s="9" t="s">
         <v>770</v>
       </c>
-      <c r="O91" s="9" t="s">
-        <v>771</v>
-      </c>
       <c r="P91" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="X91" s="1">
         <v>0</v>
@@ -9756,46 +9780,46 @@
         <v>1</v>
       </c>
       <c r="C92" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F92" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="D92" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F92" s="8" t="s">
-        <v>214</v>
-      </c>
       <c r="G92" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="J92" s="8" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K92" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="L92" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="L92" s="8" t="s">
-        <v>431</v>
-      </c>
       <c r="M92" s="9" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="N92" s="9" t="s">
+        <v>771</v>
+      </c>
+      <c r="O92" s="9" t="s">
         <v>772</v>
       </c>
-      <c r="O92" s="9" t="s">
-        <v>773</v>
-      </c>
       <c r="P92" s="9" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="X92" s="1">
         <v>0</v>
@@ -9809,46 +9833,46 @@
         <v>1</v>
       </c>
       <c r="C93" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F93" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="D93" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E93" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F93" s="8" t="s">
-        <v>216</v>
-      </c>
       <c r="G93" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="J93" s="8" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K93" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="L93" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="M93" s="9" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="N93" s="9" t="s">
+        <v>773</v>
+      </c>
+      <c r="O93" s="9" t="s">
         <v>774</v>
       </c>
-      <c r="O93" s="9" t="s">
-        <v>775</v>
-      </c>
       <c r="P93" s="9" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="X93" s="1">
         <v>0</v>
@@ -9862,46 +9886,46 @@
         <v>1</v>
       </c>
       <c r="C94" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F94" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="D94" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F94" s="8" t="s">
-        <v>218</v>
-      </c>
       <c r="G94" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="J94" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K94" s="8" t="s">
         <v>23</v>
       </c>
       <c r="L94" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M94" s="9" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="N94" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="O94" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="O94" s="9" t="s">
+      <c r="P94" s="9" t="s">
         <v>777</v>
-      </c>
-      <c r="P94" s="9" t="s">
-        <v>778</v>
       </c>
       <c r="X94" s="1">
         <v>0</v>
@@ -9915,46 +9939,46 @@
         <v>2</v>
       </c>
       <c r="C95" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F95" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="D95" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F95" s="8" t="s">
-        <v>220</v>
-      </c>
       <c r="G95" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K95" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L95" s="8" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M95" s="9" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="N95" s="9" t="s">
+        <v>778</v>
+      </c>
+      <c r="O95" s="9" t="s">
         <v>779</v>
       </c>
-      <c r="O95" s="9" t="s">
-        <v>780</v>
-      </c>
       <c r="P95" s="9" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="X95" s="1">
         <v>0</v>
@@ -9968,46 +9992,46 @@
         <v>2</v>
       </c>
       <c r="C96" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F96" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="D96" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E96" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>222</v>
-      </c>
       <c r="G96" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="J96" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K96" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L96" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M96" s="9" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="N96" s="9" t="s">
+        <v>780</v>
+      </c>
+      <c r="O96" s="9" t="s">
         <v>781</v>
       </c>
-      <c r="O96" s="9" t="s">
-        <v>782</v>
-      </c>
       <c r="P96" s="9" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="X96" s="1">
         <v>0</v>
@@ -10021,46 +10045,46 @@
         <v>2</v>
       </c>
       <c r="C97" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F97" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="D97" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E97" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F97" s="8" t="s">
-        <v>224</v>
-      </c>
       <c r="G97" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="J97" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K97" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L97" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M97" s="9" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="N97" s="9" t="s">
+        <v>782</v>
+      </c>
+      <c r="O97" s="9" t="s">
         <v>783</v>
       </c>
-      <c r="O97" s="9" t="s">
-        <v>784</v>
-      </c>
       <c r="P97" s="9" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="X97" s="1">
         <v>1</v>
@@ -10074,46 +10098,46 @@
         <v>2</v>
       </c>
       <c r="C98" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F98" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="D98" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F98" s="8" t="s">
-        <v>226</v>
-      </c>
       <c r="G98" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="J98" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K98" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L98" s="8" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="M98" s="9">
         <v>0</v>
       </c>
       <c r="N98" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="O98" s="9" t="s">
         <v>785</v>
       </c>
-      <c r="O98" s="9" t="s">
-        <v>786</v>
-      </c>
       <c r="P98" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="X98" s="1">
         <v>0</v>
@@ -10127,46 +10151,46 @@
         <v>1</v>
       </c>
       <c r="C99" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F99" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="D99" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E99" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>228</v>
-      </c>
       <c r="G99" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>910</v>
+        <v>954</v>
       </c>
       <c r="J99" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K99" s="8" t="s">
         <v>0</v>
       </c>
       <c r="L99" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="M99" s="9" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="N99" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="O99" s="9" t="s">
         <v>787</v>
       </c>
-      <c r="O99" s="9" t="s">
-        <v>788</v>
-      </c>
       <c r="P99" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="X99" s="1">
         <v>0</v>
@@ -10180,46 +10204,46 @@
         <v>2</v>
       </c>
       <c r="C100" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F100" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="D100" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E100" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F100" s="8" t="s">
-        <v>230</v>
-      </c>
       <c r="G100" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="J100" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K100" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L100" s="8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="M100" s="9" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="N100" s="9" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="O100" s="9" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="P100" s="9" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="X100" s="1">
         <v>0</v>
@@ -10233,46 +10257,46 @@
         <v>2</v>
       </c>
       <c r="C101" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F101" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="D101" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E101" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F101" s="8" t="s">
-        <v>232</v>
-      </c>
       <c r="G101" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="M101" s="9" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="N101" s="9" t="s">
+        <v>789</v>
+      </c>
+      <c r="O101" s="9" t="s">
         <v>790</v>
       </c>
-      <c r="O101" s="9" t="s">
-        <v>791</v>
-      </c>
       <c r="P101" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="X101" s="1">
         <v>0</v>
@@ -10286,46 +10310,46 @@
         <v>2</v>
       </c>
       <c r="C102" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F102" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="D102" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E102" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F102" s="8" t="s">
-        <v>234</v>
-      </c>
       <c r="G102" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K102" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L102" s="8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M102" s="9" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="N102" s="9" t="s">
+        <v>791</v>
+      </c>
+      <c r="O102" s="9" t="s">
         <v>792</v>
       </c>
-      <c r="O102" s="9" t="s">
+      <c r="P102" s="9" t="s">
         <v>793</v>
-      </c>
-      <c r="P102" s="9" t="s">
-        <v>794</v>
       </c>
       <c r="X102" s="1">
         <v>1</v>
@@ -10339,46 +10363,46 @@
         <v>2</v>
       </c>
       <c r="C103" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F103" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="D103" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E103" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F103" s="8" t="s">
-        <v>236</v>
-      </c>
       <c r="G103" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J103" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K103" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L103" s="8" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="M103" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="N103" s="9" t="s">
+        <v>794</v>
+      </c>
+      <c r="O103" s="9" t="s">
         <v>795</v>
       </c>
-      <c r="O103" s="9" t="s">
-        <v>796</v>
-      </c>
       <c r="P103" s="9" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="X103" s="1">
         <v>0</v>
@@ -10392,46 +10416,46 @@
         <v>2</v>
       </c>
       <c r="C104" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F104" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="D104" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F104" s="8" t="s">
-        <v>238</v>
-      </c>
       <c r="G104" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="J104" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K104" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L104" s="8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M104" s="9">
         <v>0</v>
       </c>
       <c r="N104" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="O104" s="9" t="s">
         <v>797</v>
       </c>
-      <c r="O104" s="9" t="s">
-        <v>798</v>
-      </c>
       <c r="P104" s="9" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="X104" s="1">
         <v>0</v>
@@ -10445,46 +10469,46 @@
         <v>2</v>
       </c>
       <c r="C105" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F105" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="D105" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E105" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F105" s="8" t="s">
-        <v>240</v>
-      </c>
       <c r="G105" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="J105" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K105" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L105" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="M105" s="9" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="N105" s="9" t="s">
+        <v>798</v>
+      </c>
+      <c r="O105" s="9" t="s">
         <v>799</v>
       </c>
-      <c r="O105" s="9" t="s">
-        <v>800</v>
-      </c>
       <c r="P105" s="9" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="X105" s="1">
         <v>0</v>
@@ -10498,46 +10522,46 @@
         <v>2</v>
       </c>
       <c r="C106" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F106" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="D106" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E106" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F106" s="8" t="s">
-        <v>242</v>
-      </c>
       <c r="G106" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="I106" s="8" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="J106" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K106" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L106" s="8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="M106" s="9">
         <v>0</v>
       </c>
       <c r="N106" s="9" t="s">
+        <v>800</v>
+      </c>
+      <c r="O106" s="9" t="s">
         <v>801</v>
       </c>
-      <c r="O106" s="9" t="s">
-        <v>802</v>
-      </c>
       <c r="P106" s="9" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="X106" s="1">
         <v>0</v>
@@ -10551,46 +10575,46 @@
         <v>2</v>
       </c>
       <c r="C107" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F107" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="D107" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E107" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F107" s="8" t="s">
-        <v>244</v>
-      </c>
       <c r="G107" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H107" s="8" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="J107" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K107" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L107" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="M107" s="9" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="N107" s="9" t="s">
+        <v>802</v>
+      </c>
+      <c r="O107" s="9" t="s">
         <v>803</v>
       </c>
-      <c r="O107" s="9" t="s">
-        <v>804</v>
-      </c>
       <c r="P107" s="9" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="X107" s="1">
         <v>0</v>
@@ -10604,46 +10628,46 @@
         <v>2</v>
       </c>
       <c r="C108" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E108" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F108" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="D108" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E108" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F108" s="8" t="s">
-        <v>246</v>
-      </c>
       <c r="G108" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H108" s="8" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J108" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K108" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L108" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="M108" s="9">
         <v>0</v>
       </c>
       <c r="N108" s="9" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="O108" s="9" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="P108" s="9" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="X108" s="1">
         <v>0</v>
@@ -10657,46 +10681,46 @@
         <v>1</v>
       </c>
       <c r="C109" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E109" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F109" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="D109" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E109" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F109" s="8" t="s">
-        <v>248</v>
-      </c>
       <c r="G109" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H109" s="8" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="J109" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K109" s="8" t="s">
         <v>0</v>
       </c>
       <c r="L109" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="M109" s="9" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="N109" s="9" t="s">
+        <v>805</v>
+      </c>
+      <c r="O109" s="9" t="s">
         <v>806</v>
       </c>
-      <c r="O109" s="9" t="s">
-        <v>807</v>
-      </c>
       <c r="P109" s="9" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="X109" s="1">
         <v>0</v>
@@ -10710,46 +10734,46 @@
         <v>2</v>
       </c>
       <c r="C110" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="D110" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F110" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="D110" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E110" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F110" s="8" t="s">
-        <v>250</v>
-      </c>
       <c r="G110" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H110" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="I110" s="10" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K110" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="L110" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="L110" s="8" t="s">
-        <v>450</v>
-      </c>
       <c r="M110" s="9" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="N110" s="9" t="s">
+        <v>807</v>
+      </c>
+      <c r="O110" s="9" t="s">
         <v>808</v>
       </c>
-      <c r="O110" s="9" t="s">
-        <v>809</v>
-      </c>
       <c r="P110" s="9" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="X110" s="1">
         <v>0</v>
@@ -10763,46 +10787,46 @@
         <v>2</v>
       </c>
       <c r="C111" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="D111" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F111" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="D111" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E111" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F111" s="8" t="s">
-        <v>252</v>
-      </c>
       <c r="G111" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H111" s="8" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J111" s="8" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K111" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="L111" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="L111" s="8" t="s">
-        <v>452</v>
-      </c>
       <c r="M111" s="9" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="X111" s="1">
         <v>0</v>
@@ -10816,46 +10840,46 @@
         <v>2</v>
       </c>
       <c r="C112" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D112" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F112" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D112" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E112" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F112" s="8" t="s">
-        <v>254</v>
-      </c>
       <c r="G112" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K112" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L112" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M112" s="9" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="N112" s="9" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="O112" s="9" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="P112" s="9" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="X112" s="1">
         <v>0</v>
@@ -10869,46 +10893,46 @@
         <v>2</v>
       </c>
       <c r="C113" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F113" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D113" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E113" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F113" s="8" t="s">
-        <v>256</v>
-      </c>
       <c r="G113" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H113" s="8" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J113" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K113" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L113" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="M113" s="9" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="N113" s="9" t="s">
+        <v>811</v>
+      </c>
+      <c r="O113" s="9" t="s">
         <v>812</v>
       </c>
-      <c r="O113" s="9" t="s">
-        <v>813</v>
-      </c>
       <c r="P113" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="X113" s="1">
         <v>0</v>
@@ -10922,46 +10946,46 @@
         <v>2</v>
       </c>
       <c r="C114" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F114" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="D114" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E114" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F114" s="8" t="s">
-        <v>258</v>
-      </c>
       <c r="G114" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="J114" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K114" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L114" s="8" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="M114" s="9" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="N114" s="9" t="s">
+        <v>813</v>
+      </c>
+      <c r="O114" s="9" t="s">
         <v>814</v>
       </c>
-      <c r="O114" s="9" t="s">
-        <v>815</v>
-      </c>
       <c r="P114" s="9" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="X114" s="1">
         <v>0</v>
@@ -10975,46 +10999,46 @@
         <v>2</v>
       </c>
       <c r="C115" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F115" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="D115" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E115" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F115" s="8" t="s">
-        <v>260</v>
-      </c>
       <c r="G115" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H115" s="8" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="J115" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K115" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L115" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="M115" s="9" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="N115" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="O115" s="9" t="s">
         <v>816</v>
       </c>
-      <c r="O115" s="9" t="s">
-        <v>817</v>
-      </c>
       <c r="P115" s="9" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="X115" s="1">
         <v>0</v>
@@ -11042,15 +11066,15 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B3" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B4" s="14">
         <v>1</v>
@@ -11066,7 +11090,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B6" s="14">
         <v>1</v>
@@ -11074,7 +11098,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B7" s="14">
         <v>8</v>
@@ -11082,7 +11106,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B8" s="14">
         <v>13</v>
@@ -11090,7 +11114,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B9" s="14">
         <v>1</v>
@@ -11098,7 +11122,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B10" s="14">
         <v>7</v>
@@ -11106,7 +11130,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B11" s="14">
         <v>1</v>
@@ -11114,7 +11138,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B12" s="14">
         <v>7</v>
@@ -11122,7 +11146,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B13" s="14">
         <v>9</v>
@@ -11138,7 +11162,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B15" s="14">
         <v>2</v>
@@ -11146,7 +11170,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B16" s="14">
         <v>2</v>
@@ -11154,7 +11178,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B17" s="14">
         <v>1</v>
@@ -11162,7 +11186,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B18" s="14">
         <v>3</v>
@@ -11186,7 +11210,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B21" s="14">
         <v>9</v>
@@ -11194,7 +11218,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B22" s="14">
         <v>1</v>
@@ -11202,7 +11226,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B23" s="14">
         <v>2</v>
@@ -11210,7 +11234,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B24" s="14">
         <v>3</v>
@@ -11218,7 +11242,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B25" s="14">
         <v>7</v>
@@ -11226,7 +11250,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B26" s="14">
         <v>7</v>
@@ -11234,7 +11258,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B27" s="14">
         <v>1</v>
@@ -11242,7 +11266,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B28" s="14">
         <v>2</v>
@@ -11250,7 +11274,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B29" s="14">
         <v>3</v>
@@ -11258,7 +11282,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B30" s="14">
         <v>2</v>
@@ -11266,7 +11290,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B31" s="14">
         <v>2</v>
@@ -11274,7 +11298,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B32" s="14">
         <v>1</v>
@@ -11282,7 +11306,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B33" s="14">
         <v>113</v>
@@ -11305,10 +11329,10 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B3" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -11321,7 +11345,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B5" s="14">
         <v>1</v>
@@ -11337,7 +11361,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B7" s="14">
         <v>1</v>
@@ -11369,7 +11393,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B11" s="14">
         <v>2</v>
@@ -11385,7 +11409,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B13" s="14">
         <v>1</v>
@@ -11393,7 +11417,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B14" s="14">
         <v>8</v>
@@ -11401,7 +11425,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B15" s="14">
         <v>13</v>
@@ -11409,7 +11433,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B16" s="14">
         <v>7</v>
@@ -11417,7 +11441,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B17" s="14">
         <v>1</v>
@@ -11425,7 +11449,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B18" s="14">
         <v>7</v>
@@ -11433,7 +11457,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B19" s="14">
         <v>9</v>
@@ -11441,7 +11465,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B20" s="14">
         <v>2</v>
@@ -11449,7 +11473,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B21" s="14">
         <v>2</v>
@@ -11457,7 +11481,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B22" s="14">
         <v>1</v>
@@ -11465,7 +11489,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B23" s="14">
         <v>3</v>
@@ -11473,7 +11497,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B24" s="14">
         <v>9</v>
@@ -11481,7 +11505,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B25" s="14">
         <v>1</v>
@@ -11489,7 +11513,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B26" s="14">
         <v>2</v>
@@ -11497,7 +11521,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B27" s="14">
         <v>3</v>
@@ -11505,7 +11529,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B28" s="14">
         <v>7</v>
@@ -11513,7 +11537,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B29" s="14">
         <v>7</v>
@@ -11521,7 +11545,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B30" s="14">
         <v>1</v>
@@ -11529,7 +11553,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B31" s="14">
         <v>2</v>
@@ -11537,7 +11561,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="15" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B32" s="14">
         <v>3</v>
@@ -11545,7 +11569,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B33" s="14">
         <v>2</v>
@@ -11553,7 +11577,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B34" s="14">
         <v>1</v>
@@ -11561,7 +11585,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B35" s="14">
         <v>113</v>
@@ -11580,13 +11604,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -11597,7 +11621,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -11608,7 +11632,7 @@
         <v>35</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -11630,7 +11654,7 @@
         <v>35</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -11652,7 +11676,7 @@
         <v>35</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -11663,7 +11687,7 @@
         <v>35</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -11685,7 +11709,7 @@
         <v>35</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -11696,7 +11720,7 @@
         <v>35</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -11707,7 +11731,7 @@
         <v>35</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -11718,7 +11742,7 @@
         <v>35</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -11729,7 +11753,7 @@
         <v>35</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -11740,7 +11764,7 @@
         <v>35</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -11751,7 +11775,7 @@
         <v>35</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -11762,7 +11786,7 @@
         <v>35</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -11773,7 +11797,7 @@
         <v>35</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -11795,7 +11819,7 @@
         <v>35</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -11806,7 +11830,7 @@
         <v>35</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -11817,7 +11841,7 @@
         <v>35</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -11828,7 +11852,7 @@
         <v>35</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -11839,7 +11863,7 @@
         <v>35</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -11850,7 +11874,7 @@
         <v>35</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -11872,7 +11896,7 @@
         <v>2</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -11883,7 +11907,7 @@
         <v>35</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -11894,7 +11918,7 @@
         <v>35</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -11905,7 +11929,7 @@
         <v>35</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -11916,7 +11940,7 @@
         <v>35</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -11927,7 +11951,7 @@
         <v>35</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -11938,7 +11962,7 @@
         <v>35</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -11949,7 +11973,7 @@
         <v>35</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -11960,7 +11984,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -11971,7 +11995,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -11982,7 +12006,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -11993,7 +12017,7 @@
         <v>35</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -12004,7 +12028,7 @@
         <v>35</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -12015,7 +12039,7 @@
         <v>35</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -12026,7 +12050,7 @@
         <v>35</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -12037,7 +12061,7 @@
         <v>35</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -12048,7 +12072,7 @@
         <v>35</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -12059,7 +12083,7 @@
         <v>35</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -12081,7 +12105,7 @@
         <v>35</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -12092,7 +12116,7 @@
         <v>35</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -12103,7 +12127,7 @@
         <v>35</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -12114,7 +12138,7 @@
         <v>35</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -12125,7 +12149,7 @@
         <v>35</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -12147,7 +12171,7 @@
         <v>35</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -12169,7 +12193,7 @@
         <v>35</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -12180,7 +12204,7 @@
         <v>35</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -12191,7 +12215,7 @@
         <v>35</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -12202,7 +12226,7 @@
         <v>35</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -12213,7 +12237,7 @@
         <v>35</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -12224,7 +12248,7 @@
         <v>35</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -12257,7 +12281,7 @@
         <v>35</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -12268,7 +12292,7 @@
         <v>35</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -12290,7 +12314,7 @@
         <v>35</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -12301,7 +12325,7 @@
         <v>35</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -12312,7 +12336,7 @@
         <v>35</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -12334,7 +12358,7 @@
         <v>35</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -12345,7 +12369,7 @@
         <v>35</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -12356,7 +12380,7 @@
         <v>35</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -12367,7 +12391,7 @@
         <v>35</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -12378,7 +12402,7 @@
         <v>35</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
@@ -12389,7 +12413,7 @@
         <v>35</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -12400,7 +12424,7 @@
         <v>35</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -12411,7 +12435,7 @@
         <v>35</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -12422,7 +12446,7 @@
         <v>35</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -12433,7 +12457,7 @@
         <v>35</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -12444,7 +12468,7 @@
         <v>35</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
@@ -12466,7 +12490,7 @@
         <v>35</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -12477,7 +12501,7 @@
         <v>35</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -12488,7 +12512,7 @@
         <v>35</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
@@ -12499,7 +12523,7 @@
         <v>35</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
@@ -12521,7 +12545,7 @@
         <v>35</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
@@ -12532,7 +12556,7 @@
         <v>35</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
@@ -12543,7 +12567,7 @@
         <v>35</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -12554,7 +12578,7 @@
         <v>35</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -12565,7 +12589,7 @@
         <v>35</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -12576,7 +12600,7 @@
         <v>2</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
@@ -12587,7 +12611,7 @@
         <v>2</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -12609,7 +12633,7 @@
         <v>35</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
@@ -12620,7 +12644,7 @@
         <v>35</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -12631,7 +12655,7 @@
         <v>35</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -12642,7 +12666,7 @@
         <v>35</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
@@ -12664,7 +12688,7 @@
         <v>35</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
@@ -12675,7 +12699,7 @@
         <v>35</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
@@ -12686,7 +12710,7 @@
         <v>35</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
@@ -12697,7 +12721,7 @@
         <v>35</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
@@ -12708,7 +12732,7 @@
         <v>35</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
@@ -12719,7 +12743,7 @@
         <v>35</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
@@ -12730,7 +12754,7 @@
         <v>35</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
@@ -12741,7 +12765,7 @@
         <v>35</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
@@ -12752,7 +12776,7 @@
         <v>35</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
@@ -12774,7 +12798,7 @@
         <v>35</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
@@ -12785,7 +12809,7 @@
         <v>35</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
@@ -12796,7 +12820,7 @@
         <v>35</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
@@ -12807,7 +12831,7 @@
         <v>35</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -12818,7 +12842,7 @@
         <v>35</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
@@ -12829,7 +12853,7 @@
         <v>35</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
